--- a/excel-negocios/caso_los_robles.xlsx
+++ b/excel-negocios/caso_los_robles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santilara/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santilara/Documents/Codex/2026-09-30/es/outputs/portafolio-datos-negocios/excel-negocios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB940A8C-AFAE-AE47-8D5D-1255857D1468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E82F2B-CD95-244A-8423-49486DE2BB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40" yWindow="660" windowWidth="30240" windowHeight="18000" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0 - Portada" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,9 @@
   <definedNames>
     <definedName name="Slicer_Trim">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="351">
   <si>
     <t>PROYECTO EVALUADOR 2 — FERRETERIA LOS ROBLES — VERSION 01</t>
   </si>
@@ -624,13 +624,7 @@
     <t>R2-P1: Cuantas transacciones Premium tiene su version en total? Que porcentaje del total representan?</t>
   </si>
   <si>
-    <t>El total de transacciones Premium (ventas de 500,000 colones o mas) en esta version es de 8 sobre las 90 transacciones registradas, lo que representa un 8.9% del total. Es la clasificacion menos frecuente de las tres, lo que confirma que las ventas grandes son la excepcion y no la norma en el patron de esta ferreteria.</t>
-  </si>
-  <si>
     <t>R2-P2: Cual sucursal concentra mas transacciones Basico? Proponga una hipotesis que explique por que podria estar ocurriendo eso.</t>
-  </si>
-  <si>
-    <t>La sucursal que concentra mas transacciones Basico (ventas menores a 200,000 colones) es Liberia, con 17 de sus 18 transacciones en esa categoria. Una hipotesis razonable es que Liberia, al estar mas alejada de la Gran Area Metropolitana, atiende un mercado con menor poder adquisitivo o con proyectos de construccion mas pequenos, y que su mezcla de productos esta concentrada en articulos de plomeria de bajo valor unitario en lugar de productos de mayor ticket como herramientas electricas o materiales al por mayor.</t>
   </si>
   <si>
     <t>R2-P3: Si la empresa quisiera mover transacciones de la categoria Basico a Regular, que estrategia operativa recomendaria?</t>
@@ -703,9 +697,6 @@
     <t>R3-P1: Cual sucursal tiene el promedio mas alto? Cual el mas bajo? Que diferencia hay entre ambas en terminos absolutos y porcentuales?</t>
   </si>
   <si>
-    <t>La sucursal con el promedio mas alto es Heredia, con 622,450 colones por transaccion, mientras que la mas baja es Liberia, con 67,594 colones. La diferencia absoluta entre ambas es de 554,856 colones, lo que equivale a que el promedio de Heredia es aproximadamente 9.2 veces mayor que el de Liberia (un 821% mas alto en terminos porcentuales).</t>
-  </si>
-  <si>
     <t>R3-P2: Encuentre una sucursal donde la mediana sea notablemente diferente al promedio. Que le indica esa diferencia sobre la distribucion de las ventas en esa sucursal?</t>
   </si>
   <si>
@@ -715,13 +706,7 @@
     <t>R3-P3: Cual sucursal tiene la desviacion estandar mas alta? Que significa eso para la predictibilidad de sus ventas mes a mes?</t>
   </si>
   <si>
-    <t>Heredia tiene la desviacion estandar mas alta, con 854,389 colones. Esto significa que sus ventas mes a mes son las menos predecibles de las cinco sucursales: el monto de una transaccion tipica puede variar enormemente de una venta a otra, lo que dificulta proyectar ingresos estables y sugiere que Heredia depende de clientes puntuales de alto volumen en lugar de un flujo constante de ventas.</t>
-  </si>
-  <si>
     <t>R3-P4: Con base en estas estadisticas, cual sucursal elegiria para un piloto de programa de incentivos de ventas? Justifique con al menos dos indicadores numericos.</t>
-  </si>
-  <si>
-    <t>Para un piloto de programa de incentivos elegiria Cartago. Aunque Heredia tiene el promedio mas alto, su resultado esta distorsionado por unas pocas ventas atipicas y su altisima desviacion estandar (854,389) hace dificil medir el efecto real del incentivo. Cartago, en cambio, tiene un promedio solido (210,956), una mediana cercana a su promedio (135,750) y una desviacion estandar mas controlada (197,712) frente a su nivel de ventas, lo que la convierte en un entorno mas estable y predecible para medir con claridad si el incentivo mejora el desempeno de los vendedores.</t>
   </si>
   <si>
     <t>RETO 4 — TABLA DINAMICA CON CAMPO CALCULADO Y SEGMENTADOR</t>
@@ -750,9 +735,6 @@
     <t>R4-P2: Cual sucursal tiene el margen mas alto segun el campo calculado? Y el mas bajo? Que diferencia de puntos porcentuales hay entre ambas?</t>
   </si>
   <si>
-    <t>Segun el campo calculado de Margen, las cinco sucursales muestran practicamente el mismo margen bruto, todas alrededor del 40.0% (entre 40.00% y 40.01%). La diferencia entre la sucursal con el margen mas alto (Liberia) y la mas baja (Heredia) es de apenas 0.01 puntos porcentuales, una diferencia insignificante. Esto ocurre porque el catalogo de productos mantiene una relacion costo/precio fija del 60% en los 30 productos, por lo que el margen no depende de que se venda sino unicamente del volumen vendido.</t>
-  </si>
-  <si>
     <t>R4-P3: Al filtrar con el segmentador solo el trimestre T3, que sucursal o categoria se destaca de forma distinta a lo que muestra el total anual?</t>
   </si>
   <si>
@@ -762,9 +744,6 @@
     <t>R4-P4: Considerando tanto el volumen de ventas como el margen, que combinacion sucursal-categoria recomendaria priorizar para maximizar la rentabilidad? Argumente con numeros concretos.</t>
   </si>
   <si>
-    <t>Como el margen es practicamente identico en todas las combinaciones (~40%), la decision debe basarse en el volumen: la combinacion Heredia-Herramientas es la que deberia priorizarse, ya que concentra el mayor volumen de ventas (11,357,109 colones, un 34% del total de la empresa) sin sacrificar margen frente a las demas sucursales. Enfocar inventario, personal y campanas de venta en esa combinacion maximiza la rentabilidad absoluta de la empresa.</t>
-  </si>
-  <si>
     <t>RETO 5 — ANALISIS FINANCIERO: PAGO, VAN Y TIR</t>
   </si>
   <si>
@@ -772,9 +751,6 @@
   </si>
   <si>
     <t>PARTE A — CREDITO PARA EXPANSION DE BODEGA</t>
-  </si>
-  <si>
-    <t>COMO USAR PAGO(): Esta funcion calcula la cuota fija de un prestamo de pago periodico constante. Sintaxis: =PAGO(tasa, nper, va). tasa es la tasa de interes del periodo (en este caso mensual), nper es el numero total de periodos (meses), va es el valor actual o monto del prestamo — ingreselo con signo negativo porque representa un desembolso. El resultado sera positivo y representa la cuota que se paga cada mes. Asegurese de que la tasa y el plazo esten en la misma unidad de tiempo (ambos mensuales o ambos anuales).</t>
   </si>
   <si>
     <t>Monto del credito (colones)</t>
@@ -848,22 +824,13 @@
     <t>R5-P4: Si la tasa mensual del credito de la Parte A subiera al 1.8%, cuanto cambiaria la cuota? Calcule la diferencia en colones y en porcentaje. Es un cambio significativo para el negocio?</t>
   </si>
   <si>
-    <t>Si la tasa mensual subiera de 1.2% a 1.8%, la cuota pasaria de 550,551 a 625,786 colones, un aumento de 75,235 colones mensuales, equivalente a un incremento del 13.67%. Es un cambio significativo para el negocio: el sobrante mensual (actualmente 99,449 colones frente a un flujo disponible de 650,000) casi desaparece, quedando solo 24,214 colones libres al mes, lo que dejaria a la empresa con muy poco margen ante cualquier imprevisto.</t>
-  </si>
-  <si>
     <t>RETO 6 — DASHBOARD EJECUTIVO Y ANALISIS GRUPAL</t>
   </si>
   <si>
     <t>ENUNCIADO: Construya dos graficos estrategicos con los datos pre-calculados de esta hoja y responda las cuatro preguntas de analisis. Nota: el analisis escrito INDIVIDUAL es un documento separado — ver hoja Analisis_Individual.</t>
   </si>
   <si>
-    <t>TABLA 1 — VENTAS TOTALES POR SUCURSAL Y TRIMESTRE</t>
-  </si>
-  <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>TABLA 2 — MARGEN BRUTO POR CATEGORIA</t>
   </si>
   <si>
     <t>Margen (%)</t>
@@ -889,21 +856,12 @@
     <t>R6-P2 GRUPAL: Analizando la evolucion T1 a T4 en la Tabla 1, que tendencia general observa? Hubo crecimiento sostenido, caida o comportamiento irregular? Que deberia anticipar la empresa para el proximo ciclo?</t>
   </si>
   <si>
-    <t>La evolucion de T1 a T4 es irregular, no hay un crecimiento ni una caida sostenida: las ventas totales de la empresa pasan de 6,860,150 en T1 a 6,122,700 en T2, caen fuertemente a 3,481,650 en T3 y se recuperan a 6,674,800 en T4. El trimestre que rompe el patron es T3, donde las ventas totales caen a menos de la mitad del nivel de T1 en casi todas las sucursales. La empresa deberia anticipar una desaceleracion estacional en T3 (posiblemente por factores como vacaciones o menor actividad de construccion) y planificar su flujo de caja e inventario para cubrir ese periodo mas debil.</t>
-  </si>
-  <si>
     <t>R6-P3 GRUPAL: Segun la Tabla 2, cual categoria tiene el margen mas alto? Que estrategia concreta recomendaria para aprovechar ese margen en terminos de inventario o fuerza de ventas?</t>
   </si>
   <si>
-    <t>Segun la Tabla 2, el margen bruto es practicamente identico en las cinco categorias, todas alrededor del 40.0%, porque el catalogo mantiene una relacion costo/precio fija del 60% en todos los productos. Al no existir una categoria con margen superior, la estrategia mas efectiva no es buscar margen sino volumen: concentrar inventario y fuerza de ventas en Herramientas, que es la categoria (y sucursal) con mayor volumen de ventas en colones, para maximizar la ganancia bruta total sin sacrificar margen.</t>
-  </si>
-  <si>
     <t>R6-P4 GRUPAL: Si la empresa tuviera que cerrar la sucursal o descontinuar la categoria de menor desempeno, cual elegiria y por que? Sustente con datos de al menos dos retos diferentes.</t>
   </si>
   <si>
-    <t>Si la empresa tuviera que cerrar una sucursal o descontinuar una categoria, la eleccion mas razonable seria Liberia / Plomeria: segun el Reto 3, Liberia tiene el promedio de venta mas bajo de las cinco sucursales (67,594 colones) y la mayor concentracion de transacciones Basico segun el Reto 2 (17 de 18 transacciones por debajo de 200,000 colones). Ademas, segun esta Tabla 1, Liberia genera el menor volumen total del ano (1,216,700 colones), muy por debajo de las demas sucursales. Con margen uniforme entre categorias, no hay ninguna ventaja de rentabilidad que compense su bajo volumen, por lo que es la opcion con menor impacto negativo si se debe reducir operaciones.</t>
-  </si>
-  <si>
     <t>RECORDATORIO: Las respuestas anteriores son del trio. El analisis escrito INDIVIDUAL tiene sus propias 4 preguntas en la hoja Analisis_Individual y se entrega como documento separado.</t>
   </si>
   <si>
@@ -1027,9 +985,6 @@
     <t>Ejemplo de pregunta: 'En PAGO, por que el monto del prestamo va con signo negativo?'</t>
   </si>
   <si>
-    <t>Respuesta solida: 'Porque PAGO sigue la convencion financiera de Excel: los flujos que salen (dinero que usted recibe como prestamo es una entrada, pero la empresa lo ve como una obligacion futura). Al ponerlo negativo, Excel devuelve la cuota como un numero positivo, que es lo que paga el negocio cada mes. Si no se pone el negativo, la cuota sale como numero negativo, lo que seria confuso en el contexto del analisis.'</t>
-  </si>
-  <si>
     <t>BLOQUE 2 — INTERPRETACION DE RESULTADOS: EJEMPLOS CON NUMEROS HIPOTETICOS</t>
   </si>
   <si>
@@ -1118,6 +1073,57 @@
   </si>
   <si>
     <t>Sum of margen</t>
+  </si>
+  <si>
+    <t>Hay 8 transacciones Premium de las 90 registradas (8.9%). Su participación describe la frecuencia de compras de ₡500.000 o más en esta muestra.</t>
+  </si>
+  <si>
+    <t>Liberia concentra 17 transacciones Básico de sus 18 registros. Una hipótesis es que su mezcla de productos o cantidades por compra favorezca tickets menores. Los datos no permiten atribuirlo al poder adquisitivo de sus clientes.</t>
+  </si>
+  <si>
+    <t>Heredia tiene el promedio más alto: ₡622.450 por transacción. Liberia tiene el menor: ₡67.594. La diferencia es de ₡554.856; Heredia equivale a 9,21 veces Liberia, aproximadamente un 820,9% más.</t>
+  </si>
+  <si>
+    <t>Heredia presenta la mayor desviación estándar por transacción: ₡854.389. Esto indica alta dispersión entre compras individuales. Para evaluar la estabilidad mes a mes es necesario agregar las ventas por mes; esta estadística por transacción no demuestra por sí sola la predictibilidad mensual.</t>
+  </si>
+  <si>
+    <t>Propondría Cartago para un piloto: su promedio por transacción es ₡210.956, su mediana ₡135.750 y su desviación estándar ₡197.712, menor que la de Heredia (₡854.389). Es una propuesta que requiere un grupo de comparación y medición antes y después; estas cifras no garantizan estabilidad mensual ni el efecto del incentivo.</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>n.a.: margen no aplicable cuando no hay ventas en la combinación filtrada.</t>
+  </si>
+  <si>
+    <t>Liberia presenta el mayor margen bruto (40,0130%) y Heredia el menor (40,0022%). La diferencia es de 0,0109 puntos porcentuales. Los márgenes son muy próximos al 40% en esta base; la contribución bruta en colones depende principalmente del volumen vendido, mientras que el porcentaje no aumenta por vender más.</t>
+  </si>
+  <si>
+    <t>Priorizaría el análisis de Heredia–Herramientas: vende ₡11,357,109, el 48.8% del total de esta base, con un margen cercano al 40%. Antes de ampliar inventario o personal, evaluaría demanda, rotación y costos operativos. La mayor utilidad bruta observada no garantiza por sí sola la máxima rentabilidad neta.</t>
+  </si>
+  <si>
+    <t>PAGO(tasa, nper, va) calcula una cuota periódica constante. La tasa y el plazo deben usar la misma unidad. En este ejercicio se usa -monto como valor actual para mostrar la cuota como un importe positivo; los signos representan sentidos opuestos del flujo.</t>
+  </si>
+  <si>
+    <t>Al subir la tasa mensual del 1,2% al 1,8%, la cuota pasa de ₡550,551 a ₡625,786: aumenta ₡75,235 (13.67%). Con ₡650.000 disponibles quedarían ₡24,214 al mes. El cálculo mantiene el plazo de 48 meses y no incluye comisiones ni seguros.</t>
+  </si>
+  <si>
+    <t>TABLA 1 — VENTAS POR SUCURSAL Y TRIMESTRE (BASE RETO 1)</t>
+  </si>
+  <si>
+    <t>TABLA 2 — MARGEN BRUTO POR CATEGORÍA (BASE RETO 4)</t>
+  </si>
+  <si>
+    <t>Los totales por trimestre son ₡6.860.150 (T1), ₡6.122.700 (T2), ₡3.481.650 (T3) y ₡6.674.800 (T4). T3 cae un 49,25% respecto de T1 y T4 se recupera. El patrón de este único año es irregular; no prueba estacionalidad ni permite atribuir la caída a vacaciones o clima. Conviene investigar sus causas y simular el efecto de un trimestre débil sobre caja e inventario.</t>
+  </si>
+  <si>
+    <t>En la base del Reto 4, Plomería tiene el margen más alto (40,0130%), apenas 0,0109 puntos porcentuales sobre Herramientas. Herramientas aporta el mayor volumen de ventas, ₡11.357.109. Propondría analizar su reposición según demanda y rotación; no justificaría una decisión comercial en una diferencia de margen tan pequeña.</t>
+  </si>
+  <si>
+    <t>Liberia merece una revisión operativa: registra ₡1.216.700 de ventas en la base del Reto 1, un promedio de ₡67.594 por transacción en el Reto 3 y 17 de 18 compras Básico en el Reto 2. Estos indicadores no bastan para recomendar un cierre. Se necesitan costos fijos, utilidad neta, cobertura comercial y demanda potencial antes de decidir.</t>
+  </si>
+  <si>
+    <t>En PAGO, el valor actual y las cuotas tienen signos opuestos por la convención de flujos. Si registramos el préstamo recibido como positivo, las cuotas son negativas. Aquí se usa -monto para presentar la cuota como un importe positivo de pago.</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1131,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1537,43 +1543,80 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1582,49 +1625,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1633,32 +1651,11 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="276">
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
+  <dxfs count="58">
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
@@ -1711,721 +1708,76 @@
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="&quot;₡&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="&quot;₡&quot;#,##0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="&quot;₡&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <numFmt numFmtId="164" formatCode="&quot;₡&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
@@ -2514,7 +1866,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2832,7 +2184,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -2850,7 +2202,7 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -2868,7 +2220,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -2887,7 +2239,7 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2900,7 +2252,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
@@ -2937,21 +2289,11 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.3117283950617286E-2"/>
-          <c:y val="0"/>
-          <c:w val="0.95688271604938269"/>
-          <c:h val="0.90869281045751638"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3046,7 +2388,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -3064,7 +2406,7 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -3081,8 +2423,10 @@
         <c:axId val="100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="0.5"/>
+          <c:min val="0"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -3101,7 +2445,7 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3139,8 +2483,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>40361</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Trim">
@@ -3163,7 +2507,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3330,7 +2674,7 @@
     <cacheField name="Total Costo" numFmtId="3">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="492" maxValue="1799952"/>
     </cacheField>
-    <cacheField name="margen" numFmtId="0" formula=" ('Total Venta' -'Total Costo' )/'Total Venta'" databaseField="0"/>
+    <cacheField name="margen" numFmtId="0" formula=" ('Total Venta'-'Total Costo')/'Total Venta'" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -4516,7 +3860,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2BB0B1F2-2FB4-244D-8A26-33BFE449C922}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2BB0B1F2-2FB4-244D-8A26-33BFE449C922}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" errorCaption="n.a." showError="1" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="R6:AD14" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -4633,45 +3977,45 @@
     <dataField name="Sum of margen" fld="11" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="29">
-    <format dxfId="3">
+    <format dxfId="0">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="2">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="3">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="4">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="5">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="6">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="10">
       <pivotArea field="4" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4680,11 +4024,50 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="11">
       <pivotArea field="4" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
@@ -4697,7 +4080,7 @@
             <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
-            <x v="0"/>
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -4710,51 +4093,12 @@
             <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
-            <x v="1"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
     </format>
     <format dxfId="17">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="20">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4769,7 +4113,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4784,7 +4128,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="19">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4799,7 +4143,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="20">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4814,7 +4158,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="21">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4829,7 +4173,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="22">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4841,7 +4185,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="23">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4853,7 +4197,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="24">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4865,7 +4209,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="25">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4877,7 +4221,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="26">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -4889,7 +4233,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="27">
       <pivotArea grandRow="1" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4898,7 +4242,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="28">
       <pivotArea field="3" grandCol="1" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5243,205 +4587,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="31"/>
     </row>
     <row r="3" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="27"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
     </row>
     <row r="11" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="31"/>
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="40"/>
     </row>
     <row r="14" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="40"/>
     </row>
     <row r="15" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="40"/>
     </row>
     <row r="16" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="27"/>
+      <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="27"/>
+      <c r="C20" s="31"/>
     </row>
     <row r="21" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="27"/>
+      <c r="C21" s="31"/>
     </row>
     <row r="22" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="27"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="27"/>
+      <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="27"/>
+      <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="27"/>
+      <c r="C25" s="31"/>
     </row>
     <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="27"/>
+      <c r="C26" s="31"/>
     </row>
     <row r="27" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="27"/>
+      <c r="C27" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B6:C6"/>
@@ -5453,17 +4807,7 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5483,292 +4827,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
-        <v>308</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="56" t="s">
+        <v>294</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="61" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
     </row>
     <row r="3" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="51" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
+      <c r="A4" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27"/>
+      <c r="A5" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31"/>
     </row>
     <row r="6" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="58" t="s">
-        <v>312</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="61" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="57" t="s">
-        <v>315</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
     </row>
     <row r="12" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="58" t="s">
-        <v>316</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="61" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
     </row>
     <row r="13" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="57" t="s">
-        <v>317</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
+      <c r="A14" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
     </row>
     <row r="15" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="58" t="s">
-        <v>318</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="61" t="s">
+        <v>350</v>
+      </c>
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
     </row>
     <row r="16" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="59" t="s">
-        <v>319</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="57" t="s">
-        <v>320</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="58" t="s">
-        <v>321</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="27"/>
+      <c r="A20" s="61" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
     </row>
     <row r="21" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="57" t="s">
-        <v>322</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="27"/>
+      <c r="A22" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="58" t="s">
-        <v>323</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="61" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
+      <c r="A25" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
     </row>
     <row r="26" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="58" t="s">
-        <v>325</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
+      <c r="A26" s="61" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
     </row>
     <row r="27" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="57" t="s">
-        <v>326</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
+      <c r="A28" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
     </row>
     <row r="29" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="58" t="s">
-        <v>327</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
+      <c r="A29" s="61" t="s">
+        <v>312</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
     </row>
     <row r="30" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
+      <c r="A32" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
     </row>
     <row r="33" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="57" t="s">
-        <v>329</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
+      <c r="A33" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
     </row>
     <row r="34" spans="1:3" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="58" t="s">
-        <v>330</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
+      <c r="A34" s="61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B34" s="30"/>
+      <c r="C34" s="31"/>
     </row>
     <row r="35" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="57" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
+      <c r="A36" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
     </row>
     <row r="37" spans="1:3" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="58" t="s">
-        <v>332</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
+      <c r="A37" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="39" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="62" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" s="30"/>
+      <c r="C39" s="31"/>
     </row>
     <row r="40" spans="1:3" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="31"/>
     </row>
     <row r="41" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="42" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="62" t="s">
-        <v>335</v>
-      </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="27"/>
+      <c r="A43" s="64" t="s">
+        <v>320</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="31"/>
     </row>
     <row r="44" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="53" t="s">
-        <v>336</v>
-      </c>
-      <c r="B44" s="26"/>
-      <c r="C44" s="27"/>
+      <c r="A44" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="B44" s="30"/>
+      <c r="C44" s="31"/>
     </row>
     <row r="45" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="46" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="B46" s="26"/>
-      <c r="C46" s="27"/>
+      <c r="A46" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="31"/>
     </row>
     <row r="47" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="53" t="s">
-        <v>338</v>
-      </c>
-      <c r="B48" s="26"/>
-      <c r="C48" s="27"/>
+      <c r="A48" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="B48" s="30"/>
+      <c r="C48" s="31"/>
     </row>
     <row r="49" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="50" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="53" t="s">
-        <v>339</v>
-      </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="27"/>
+      <c r="A50" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="B50" s="30"/>
+      <c r="C50" s="31"/>
     </row>
     <row r="51" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="52" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="27"/>
+      <c r="A52" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="31"/>
     </row>
     <row r="53" spans="1:3" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="55" spans="1:3" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="60" t="s">
-        <v>341</v>
-      </c>
-      <c r="B55" s="26"/>
-      <c r="C55" s="27"/>
+      <c r="A55" s="66" t="s">
+        <v>326</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A18:C18"/>
@@ -5777,6 +5095,32 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5797,22 +5141,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
@@ -6372,181 +5716,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="31"/>
     </row>
     <row r="2" spans="1:13" ht="64" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="31"/>
     </row>
     <row r="3" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="27"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="31"/>
     </row>
     <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="34"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="40"/>
     </row>
     <row r="6" spans="1:13" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44">
+      <c r="A6" s="38">
         <f>COUNTIF(D18:D107,"Central")</f>
         <v>18</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="34"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="40"/>
     </row>
     <row r="7" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="34"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="40"/>
     </row>
     <row r="9" spans="1:13" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="44">
+      <c r="A9" s="38">
         <f>SUM(L18:L107)</f>
         <v>23139300</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="34"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="40"/>
     </row>
     <row r="10" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="60" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="34"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="40"/>
     </row>
     <row r="12" spans="1:13" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="34"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="40"/>
     </row>
     <row r="13" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:13" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="47"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59"/>
     </row>
     <row r="16" spans="1:13" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9618,7 +8962,7 @@
         <v>107</v>
       </c>
       <c r="G82" s="4" t="str">
-        <f t="shared" ref="G82:G113" si="6">TRIM(F82)</f>
+        <f t="shared" ref="G82:G107" si="6">TRIM(F82)</f>
         <v>PLO-005</v>
       </c>
       <c r="H82" s="4" t="str">
@@ -10856,142 +10200,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="34"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" ht="94" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="34"/>
+      <c r="A6" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
     </row>
     <row r="7" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="34"/>
+      <c r="A8" s="60" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
     </row>
     <row r="9" spans="1:8" ht="119" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="34"/>
+      <c r="A9" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
     </row>
     <row r="10" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="34"/>
+      <c r="A11" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="34"/>
+      <c r="A12" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="13" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:8" ht="177" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
+      <c r="A15" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
     </row>
     <row r="16" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27"/>
+      <c r="A17" s="52" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
@@ -11013,27 +10357,33 @@
         <v>128</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
+        <f>Reto1_Datos!A18</f>
         <v>1</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>133</v>
+      <c r="B19" s="7" t="str">
+        <f>Reto1_Datos!B18</f>
+        <v>Enero</v>
+      </c>
+      <c r="C19" s="7" t="str">
+        <f>Reto1_Datos!C18</f>
+        <v>T1</v>
+      </c>
+      <c r="D19" s="7" t="str">
+        <f>Reto1_Datos!D18</f>
+        <v>Central</v>
+      </c>
+      <c r="E19" s="7" t="str">
+        <f>Reto1_Datos!E18</f>
+        <v>Juan Mora</v>
       </c>
       <c r="F19" s="11">
-        <v>40410</v>
+        <f>Reto1_Datos!L18</f>
+        <v>38250</v>
       </c>
       <c r="G19" s="4" t="str">
         <f t="shared" ref="G19:G50" si="0">IF(F19&gt;=500000,"Premium",IF(F19&gt;=200000,"Regular","Basico"))</f>
@@ -11042,22 +10392,28 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
+        <f>Reto1_Datos!A19</f>
         <v>2</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>137</v>
+      <c r="B20" s="7" t="str">
+        <f>Reto1_Datos!B19</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C20" s="7" t="str">
+        <f>Reto1_Datos!C19</f>
+        <v>T1</v>
+      </c>
+      <c r="D20" s="7" t="str">
+        <f>Reto1_Datos!D19</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E20" s="7" t="str">
+        <f>Reto1_Datos!E19</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F20" s="11">
-        <v>125653</v>
+        <f>Reto1_Datos!L19</f>
+        <v>132000</v>
       </c>
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11066,22 +10422,28 @@
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
+        <f>Reto1_Datos!A20</f>
         <v>3</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>140</v>
+      <c r="B21" s="7" t="str">
+        <f>Reto1_Datos!B20</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C21" s="7" t="str">
+        <f>Reto1_Datos!C20</f>
+        <v>T1</v>
+      </c>
+      <c r="D21" s="7" t="str">
+        <f>Reto1_Datos!D20</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E21" s="7" t="str">
+        <f>Reto1_Datos!E20</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F21" s="11">
-        <v>2022048</v>
+        <f>Reto1_Datos!L20</f>
+        <v>1890000</v>
       </c>
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11090,22 +10452,28 @@
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
+        <f>Reto1_Datos!A21</f>
         <v>4</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>144</v>
+      <c r="B22" s="7" t="str">
+        <f>Reto1_Datos!B21</f>
+        <v>Abril</v>
+      </c>
+      <c r="C22" s="7" t="str">
+        <f>Reto1_Datos!C21</f>
+        <v>T2</v>
+      </c>
+      <c r="D22" s="7" t="str">
+        <f>Reto1_Datos!D21</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E22" s="7" t="str">
+        <f>Reto1_Datos!E21</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F22" s="11">
-        <v>326624</v>
+        <f>Reto1_Datos!L21</f>
+        <v>304000</v>
       </c>
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11114,22 +10482,28 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
+        <f>Reto1_Datos!A22</f>
         <v>5</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>148</v>
+      <c r="B23" s="7" t="str">
+        <f>Reto1_Datos!B22</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C23" s="7" t="str">
+        <f>Reto1_Datos!C22</f>
+        <v>T2</v>
+      </c>
+      <c r="D23" s="7" t="str">
+        <f>Reto1_Datos!D22</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E23" s="7" t="str">
+        <f>Reto1_Datos!E22</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F23" s="11">
-        <v>349182</v>
+        <f>Reto1_Datos!L22</f>
+        <v>323000</v>
       </c>
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11138,22 +10512,28 @@
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
+        <f>Reto1_Datos!A23</f>
         <v>6</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>150</v>
+      <c r="B24" s="7" t="str">
+        <f>Reto1_Datos!B23</f>
+        <v>Junio</v>
+      </c>
+      <c r="C24" s="7" t="str">
+        <f>Reto1_Datos!C23</f>
+        <v>T2</v>
+      </c>
+      <c r="D24" s="7" t="str">
+        <f>Reto1_Datos!D23</f>
+        <v>Central</v>
+      </c>
+      <c r="E24" s="7" t="str">
+        <f>Reto1_Datos!E23</f>
+        <v>Ana Vargas</v>
       </c>
       <c r="F24" s="11">
-        <v>13260</v>
+        <f>Reto1_Datos!L23</f>
+        <v>13500</v>
       </c>
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11162,22 +10542,28 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
+        <f>Reto1_Datos!A24</f>
         <v>7</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>153</v>
+      <c r="B25" s="7" t="str">
+        <f>Reto1_Datos!B24</f>
+        <v>Julio</v>
+      </c>
+      <c r="C25" s="7" t="str">
+        <f>Reto1_Datos!C24</f>
+        <v>T3</v>
+      </c>
+      <c r="D25" s="7" t="str">
+        <f>Reto1_Datos!D24</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E25" s="7" t="str">
+        <f>Reto1_Datos!E24</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F25" s="11">
-        <v>85620</v>
+        <f>Reto1_Datos!L24</f>
+        <v>93000</v>
       </c>
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11186,22 +10572,28 @@
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
+        <f>Reto1_Datos!A25</f>
         <v>8</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>156</v>
+      <c r="B26" s="7" t="str">
+        <f>Reto1_Datos!B25</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C26" s="7" t="str">
+        <f>Reto1_Datos!C25</f>
+        <v>T3</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <f>Reto1_Datos!D25</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E26" s="7" t="str">
+        <f>Reto1_Datos!E25</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F26" s="11">
-        <v>262636</v>
+        <f>Reto1_Datos!L25</f>
+        <v>264000</v>
       </c>
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11210,22 +10602,28 @@
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
+        <f>Reto1_Datos!A26</f>
         <v>9</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>159</v>
+      <c r="B27" s="7" t="str">
+        <f>Reto1_Datos!B26</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C27" s="7" t="str">
+        <f>Reto1_Datos!C26</f>
+        <v>T3</v>
+      </c>
+      <c r="D27" s="7" t="str">
+        <f>Reto1_Datos!D26</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E27" s="7" t="str">
+        <f>Reto1_Datos!E26</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F27" s="11">
-        <v>301119</v>
+        <f>Reto1_Datos!L26</f>
+        <v>304200</v>
       </c>
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11234,22 +10632,28 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
+        <f>Reto1_Datos!A27</f>
         <v>10</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>162</v>
+      <c r="B28" s="7" t="str">
+        <f>Reto1_Datos!B27</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C28" s="7" t="str">
+        <f>Reto1_Datos!C27</f>
+        <v>T4</v>
+      </c>
+      <c r="D28" s="7" t="str">
+        <f>Reto1_Datos!D27</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E28" s="7" t="str">
+        <f>Reto1_Datos!E27</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F28" s="11">
-        <v>45105</v>
+        <f>Reto1_Datos!L27</f>
+        <v>48000</v>
       </c>
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11258,22 +10662,28 @@
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
+        <f>Reto1_Datos!A28</f>
         <v>11</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>165</v>
+      <c r="B29" s="7" t="str">
+        <f>Reto1_Datos!B28</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C29" s="7" t="str">
+        <f>Reto1_Datos!C28</f>
+        <v>T4</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <f>Reto1_Datos!D28</f>
+        <v>Central</v>
+      </c>
+      <c r="E29" s="7" t="str">
+        <f>Reto1_Datos!E28</f>
+        <v>Carlos Solano</v>
       </c>
       <c r="F29" s="11">
-        <v>681450</v>
+        <f>Reto1_Datos!L28</f>
+        <v>630000</v>
       </c>
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11282,22 +10692,28 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
+        <f>Reto1_Datos!A29</f>
         <v>12</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>167</v>
+      <c r="B30" s="7" t="str">
+        <f>Reto1_Datos!B29</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C30" s="7" t="str">
+        <f>Reto1_Datos!C29</f>
+        <v>T4</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f>Reto1_Datos!D29</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E30" s="7" t="str">
+        <f>Reto1_Datos!E29</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F30" s="11">
-        <v>71070</v>
+        <f>Reto1_Datos!L29</f>
+        <v>73600</v>
       </c>
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11306,22 +10722,28 @@
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
+        <f>Reto1_Datos!A30</f>
         <v>13</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>168</v>
+      <c r="B31" s="7" t="str">
+        <f>Reto1_Datos!B30</f>
+        <v>Enero</v>
+      </c>
+      <c r="C31" s="7" t="str">
+        <f>Reto1_Datos!C30</f>
+        <v>T1</v>
+      </c>
+      <c r="D31" s="7" t="str">
+        <f>Reto1_Datos!D30</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E31" s="7" t="str">
+        <f>Reto1_Datos!E30</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F31" s="11">
-        <v>61019</v>
+        <f>Reto1_Datos!L30</f>
+        <v>59500</v>
       </c>
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11330,22 +10752,28 @@
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
+        <f>Reto1_Datos!A31</f>
         <v>14</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>170</v>
+      <c r="B32" s="7" t="str">
+        <f>Reto1_Datos!B31</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C32" s="7" t="str">
+        <f>Reto1_Datos!C31</f>
+        <v>T1</v>
+      </c>
+      <c r="D32" s="7" t="str">
+        <f>Reto1_Datos!D31</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E32" s="7" t="str">
+        <f>Reto1_Datos!E31</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F32" s="11">
-        <v>135960</v>
+        <f>Reto1_Datos!L31</f>
+        <v>138600</v>
       </c>
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11354,22 +10782,28 @@
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
+        <f>Reto1_Datos!A32</f>
         <v>15</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>148</v>
+      <c r="B33" s="7" t="str">
+        <f>Reto1_Datos!B32</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C33" s="7" t="str">
+        <f>Reto1_Datos!C32</f>
+        <v>T1</v>
+      </c>
+      <c r="D33" s="7" t="str">
+        <f>Reto1_Datos!D32</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E33" s="7" t="str">
+        <f>Reto1_Datos!E32</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F33" s="11">
-        <v>6840</v>
+        <f>Reto1_Datos!L32</f>
+        <v>6750</v>
       </c>
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11378,22 +10812,28 @@
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
+        <f>Reto1_Datos!A33</f>
         <v>16</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>172</v>
+      <c r="B34" s="7" t="str">
+        <f>Reto1_Datos!B33</f>
+        <v>Abril</v>
+      </c>
+      <c r="C34" s="7" t="str">
+        <f>Reto1_Datos!C33</f>
+        <v>T2</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <f>Reto1_Datos!D33</f>
+        <v>Central</v>
+      </c>
+      <c r="E34" s="7" t="str">
+        <f>Reto1_Datos!E33</f>
+        <v>Rita Ulate</v>
       </c>
       <c r="F34" s="11">
-        <v>45136</v>
+        <f>Reto1_Datos!L33</f>
+        <v>48000</v>
       </c>
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11402,22 +10842,28 @@
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
+        <f>Reto1_Datos!A34</f>
         <v>17</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>137</v>
+      <c r="B35" s="7" t="str">
+        <f>Reto1_Datos!B34</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C35" s="7" t="str">
+        <f>Reto1_Datos!C34</f>
+        <v>T2</v>
+      </c>
+      <c r="D35" s="7" t="str">
+        <f>Reto1_Datos!D34</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E35" s="7" t="str">
+        <f>Reto1_Datos!E34</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F35" s="11">
-        <v>29547</v>
+        <f>Reto1_Datos!L34</f>
+        <v>31500</v>
       </c>
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11426,22 +10872,28 @@
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
+        <f>Reto1_Datos!A35</f>
         <v>18</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>140</v>
+      <c r="B36" s="7" t="str">
+        <f>Reto1_Datos!B35</f>
+        <v>Junio</v>
+      </c>
+      <c r="C36" s="7" t="str">
+        <f>Reto1_Datos!C35</f>
+        <v>T2</v>
+      </c>
+      <c r="D36" s="7" t="str">
+        <f>Reto1_Datos!D35</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E36" s="7" t="str">
+        <f>Reto1_Datos!E35</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F36" s="11">
-        <v>149900</v>
+        <f>Reto1_Datos!L35</f>
+        <v>156000</v>
       </c>
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11450,22 +10902,28 @@
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
+        <f>Reto1_Datos!A36</f>
         <v>19</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>144</v>
+      <c r="B37" s="7" t="str">
+        <f>Reto1_Datos!B36</f>
+        <v>Julio</v>
+      </c>
+      <c r="C37" s="7" t="str">
+        <f>Reto1_Datos!C36</f>
+        <v>T3</v>
+      </c>
+      <c r="D37" s="7" t="str">
+        <f>Reto1_Datos!D36</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E37" s="7" t="str">
+        <f>Reto1_Datos!E36</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F37" s="11">
-        <v>14256</v>
+        <f>Reto1_Datos!L36</f>
+        <v>15300</v>
       </c>
       <c r="G37" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11474,22 +10932,28 @@
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
+        <f>Reto1_Datos!A37</f>
         <v>20</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>162</v>
+      <c r="B38" s="7" t="str">
+        <f>Reto1_Datos!B37</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C38" s="7" t="str">
+        <f>Reto1_Datos!C37</f>
+        <v>T3</v>
+      </c>
+      <c r="D38" s="7" t="str">
+        <f>Reto1_Datos!D37</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E38" s="7" t="str">
+        <f>Reto1_Datos!E37</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F38" s="11">
-        <v>53514</v>
+        <f>Reto1_Datos!L37</f>
+        <v>49500</v>
       </c>
       <c r="G38" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11498,22 +10962,28 @@
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
+        <f>Reto1_Datos!A38</f>
         <v>21</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>133</v>
+      <c r="B39" s="7" t="str">
+        <f>Reto1_Datos!B38</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C39" s="7" t="str">
+        <f>Reto1_Datos!C38</f>
+        <v>T3</v>
+      </c>
+      <c r="D39" s="7" t="str">
+        <f>Reto1_Datos!D38</f>
+        <v>Central</v>
+      </c>
+      <c r="E39" s="7" t="str">
+        <f>Reto1_Datos!E38</f>
+        <v>Juan Mora</v>
       </c>
       <c r="F39" s="11">
-        <v>63289</v>
+        <f>Reto1_Datos!L38</f>
+        <v>60800</v>
       </c>
       <c r="G39" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11522,22 +10992,28 @@
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
+        <f>Reto1_Datos!A39</f>
         <v>22</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>153</v>
+      <c r="B40" s="7" t="str">
+        <f>Reto1_Datos!B39</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C40" s="7" t="str">
+        <f>Reto1_Datos!C39</f>
+        <v>T4</v>
+      </c>
+      <c r="D40" s="7" t="str">
+        <f>Reto1_Datos!D39</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E40" s="7" t="str">
+        <f>Reto1_Datos!E39</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F40" s="11">
-        <v>454624</v>
+        <f>Reto1_Datos!L39</f>
+        <v>448000</v>
       </c>
       <c r="G40" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11546,22 +11022,28 @@
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
+        <f>Reto1_Datos!A40</f>
         <v>23</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>156</v>
+      <c r="B41" s="7" t="str">
+        <f>Reto1_Datos!B40</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C41" s="7" t="str">
+        <f>Reto1_Datos!C40</f>
+        <v>T4</v>
+      </c>
+      <c r="D41" s="7" t="str">
+        <f>Reto1_Datos!D40</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E41" s="7" t="str">
+        <f>Reto1_Datos!E40</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F41" s="11">
-        <v>293340</v>
+        <f>Reto1_Datos!L40</f>
+        <v>325000</v>
       </c>
       <c r="G41" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11570,22 +11052,28 @@
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
+        <f>Reto1_Datos!A41</f>
         <v>24</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>159</v>
+      <c r="B42" s="7" t="str">
+        <f>Reto1_Datos!B41</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C42" s="7" t="str">
+        <f>Reto1_Datos!C41</f>
+        <v>T4</v>
+      </c>
+      <c r="D42" s="7" t="str">
+        <f>Reto1_Datos!D41</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E42" s="7" t="str">
+        <f>Reto1_Datos!E41</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F42" s="11">
-        <v>123195</v>
+        <f>Reto1_Datos!L41</f>
+        <v>120400</v>
       </c>
       <c r="G42" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11594,22 +11082,28 @@
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
+        <f>Reto1_Datos!A42</f>
         <v>25</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>148</v>
+      <c r="B43" s="7" t="str">
+        <f>Reto1_Datos!B42</f>
+        <v>Enero</v>
+      </c>
+      <c r="C43" s="7" t="str">
+        <f>Reto1_Datos!C42</f>
+        <v>T1</v>
+      </c>
+      <c r="D43" s="7" t="str">
+        <f>Reto1_Datos!D42</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E43" s="7" t="str">
+        <f>Reto1_Datos!E42</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F43" s="11">
-        <v>63422</v>
+        <f>Reto1_Datos!L42</f>
+        <v>68400</v>
       </c>
       <c r="G43" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11618,22 +11112,28 @@
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
+        <f>Reto1_Datos!A43</f>
         <v>26</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>150</v>
+      <c r="B44" s="7" t="str">
+        <f>Reto1_Datos!B43</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C44" s="7" t="str">
+        <f>Reto1_Datos!C43</f>
+        <v>T1</v>
+      </c>
+      <c r="D44" s="7" t="str">
+        <f>Reto1_Datos!D43</f>
+        <v>Central</v>
+      </c>
+      <c r="E44" s="7" t="str">
+        <f>Reto1_Datos!E43</f>
+        <v>Ana Vargas</v>
       </c>
       <c r="F44" s="11">
-        <v>353460</v>
+        <f>Reto1_Datos!L43</f>
+        <v>365500</v>
       </c>
       <c r="G44" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11642,22 +11142,28 @@
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
+        <f>Reto1_Datos!A44</f>
         <v>27</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>167</v>
+      <c r="B45" s="7" t="str">
+        <f>Reto1_Datos!B44</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C45" s="7" t="str">
+        <f>Reto1_Datos!C44</f>
+        <v>T1</v>
+      </c>
+      <c r="D45" s="7" t="str">
+        <f>Reto1_Datos!D44</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E45" s="7" t="str">
+        <f>Reto1_Datos!E44</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F45" s="11">
-        <v>317880</v>
+        <f>Reto1_Datos!L44</f>
+        <v>294000</v>
       </c>
       <c r="G45" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11666,22 +11172,28 @@
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
+        <f>Reto1_Datos!A45</f>
         <v>28</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>168</v>
+      <c r="B46" s="7" t="str">
+        <f>Reto1_Datos!B45</f>
+        <v>Abril</v>
+      </c>
+      <c r="C46" s="7" t="str">
+        <f>Reto1_Datos!C45</f>
+        <v>T2</v>
+      </c>
+      <c r="D46" s="7" t="str">
+        <f>Reto1_Datos!D45</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E46" s="7" t="str">
+        <f>Reto1_Datos!E45</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F46" s="11">
-        <v>140322</v>
+        <f>Reto1_Datos!L45</f>
+        <v>147000</v>
       </c>
       <c r="G46" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11690,22 +11202,28 @@
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
+        <f>Reto1_Datos!A46</f>
         <v>29</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>170</v>
+      <c r="B47" s="7" t="str">
+        <f>Reto1_Datos!B46</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C47" s="7" t="str">
+        <f>Reto1_Datos!C46</f>
+        <v>T2</v>
+      </c>
+      <c r="D47" s="7" t="str">
+        <f>Reto1_Datos!D46</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E47" s="7" t="str">
+        <f>Reto1_Datos!E46</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F47" s="11">
-        <v>25636</v>
+        <f>Reto1_Datos!L46</f>
+        <v>27550</v>
       </c>
       <c r="G47" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11714,22 +11232,28 @@
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
+        <f>Reto1_Datos!A47</f>
         <v>30</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>162</v>
+      <c r="B48" s="7" t="str">
+        <f>Reto1_Datos!B47</f>
+        <v>Junio</v>
+      </c>
+      <c r="C48" s="7" t="str">
+        <f>Reto1_Datos!C47</f>
+        <v>T2</v>
+      </c>
+      <c r="D48" s="7" t="str">
+        <f>Reto1_Datos!D47</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E48" s="7" t="str">
+        <f>Reto1_Datos!E47</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F48" s="11">
-        <v>11124</v>
+        <f>Reto1_Datos!L47</f>
+        <v>10260</v>
       </c>
       <c r="G48" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11738,22 +11262,28 @@
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
+        <f>Reto1_Datos!A48</f>
         <v>31</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>165</v>
+      <c r="B49" s="7" t="str">
+        <f>Reto1_Datos!B48</f>
+        <v>Julio</v>
+      </c>
+      <c r="C49" s="7" t="str">
+        <f>Reto1_Datos!C48</f>
+        <v>T3</v>
+      </c>
+      <c r="D49" s="7" t="str">
+        <f>Reto1_Datos!D48</f>
+        <v>Central</v>
+      </c>
+      <c r="E49" s="7" t="str">
+        <f>Reto1_Datos!E48</f>
+        <v>Carlos Solano</v>
       </c>
       <c r="F49" s="11">
-        <v>7938</v>
+        <f>Reto1_Datos!L48</f>
+        <v>7650</v>
       </c>
       <c r="G49" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11762,22 +11292,28 @@
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
+        <f>Reto1_Datos!A49</f>
         <v>32</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>137</v>
+      <c r="B50" s="7" t="str">
+        <f>Reto1_Datos!B49</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C50" s="7" t="str">
+        <f>Reto1_Datos!C49</f>
+        <v>T3</v>
+      </c>
+      <c r="D50" s="7" t="str">
+        <f>Reto1_Datos!D49</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E50" s="7" t="str">
+        <f>Reto1_Datos!E49</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F50" s="11">
-        <v>461292</v>
+        <f>Reto1_Datos!L49</f>
+        <v>468000</v>
       </c>
       <c r="G50" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11786,22 +11322,28 @@
     </row>
     <row r="51" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
+        <f>Reto1_Datos!A50</f>
         <v>33</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>140</v>
+      <c r="B51" s="7" t="str">
+        <f>Reto1_Datos!B50</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C51" s="7" t="str">
+        <f>Reto1_Datos!C50</f>
+        <v>T3</v>
+      </c>
+      <c r="D51" s="7" t="str">
+        <f>Reto1_Datos!D50</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E51" s="7" t="str">
+        <f>Reto1_Datos!E50</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F51" s="11">
-        <v>664752</v>
+        <f>Reto1_Datos!L50</f>
+        <v>720000</v>
       </c>
       <c r="G51" s="4" t="str">
         <f t="shared" ref="G51:G82" si="1">IF(F51&gt;=500000,"Premium",IF(F51&gt;=200000,"Regular","Basico"))</f>
@@ -11810,22 +11352,28 @@
     </row>
     <row r="52" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
+        <f>Reto1_Datos!A51</f>
         <v>34</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>144</v>
+      <c r="B52" s="7" t="str">
+        <f>Reto1_Datos!B51</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C52" s="7" t="str">
+        <f>Reto1_Datos!C51</f>
+        <v>T4</v>
+      </c>
+      <c r="D52" s="7" t="str">
+        <f>Reto1_Datos!D51</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E52" s="7" t="str">
+        <f>Reto1_Datos!E51</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F52" s="11">
-        <v>1383720</v>
+        <f>Reto1_Datos!L51</f>
+        <v>1520000</v>
       </c>
       <c r="G52" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11834,22 +11382,28 @@
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
+        <f>Reto1_Datos!A52</f>
         <v>35</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>148</v>
+      <c r="B53" s="7" t="str">
+        <f>Reto1_Datos!B52</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C53" s="7" t="str">
+        <f>Reto1_Datos!C52</f>
+        <v>T4</v>
+      </c>
+      <c r="D53" s="7" t="str">
+        <f>Reto1_Datos!D52</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E53" s="7" t="str">
+        <f>Reto1_Datos!E52</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F53" s="11">
-        <v>117474</v>
+        <f>Reto1_Datos!L52</f>
+        <v>119000</v>
       </c>
       <c r="G53" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11858,22 +11412,28 @@
     </row>
     <row r="54" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
+        <f>Reto1_Datos!A53</f>
         <v>36</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>172</v>
+      <c r="B54" s="7" t="str">
+        <f>Reto1_Datos!B53</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C54" s="7" t="str">
+        <f>Reto1_Datos!C53</f>
+        <v>T4</v>
+      </c>
+      <c r="D54" s="7" t="str">
+        <f>Reto1_Datos!D53</f>
+        <v>Central</v>
+      </c>
+      <c r="E54" s="7" t="str">
+        <f>Reto1_Datos!E53</f>
+        <v>Rita Ulate</v>
       </c>
       <c r="F54" s="11">
-        <v>62465</v>
+        <f>Reto1_Datos!L53</f>
+        <v>58500</v>
       </c>
       <c r="G54" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11882,22 +11442,28 @@
     </row>
     <row r="55" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
+        <f>Reto1_Datos!A54</f>
         <v>37</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>153</v>
+      <c r="B55" s="7" t="str">
+        <f>Reto1_Datos!B54</f>
+        <v>Enero</v>
+      </c>
+      <c r="C55" s="7" t="str">
+        <f>Reto1_Datos!C54</f>
+        <v>T1</v>
+      </c>
+      <c r="D55" s="7" t="str">
+        <f>Reto1_Datos!D54</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E55" s="7" t="str">
+        <f>Reto1_Datos!E54</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F55" s="11">
-        <v>147420</v>
+        <f>Reto1_Datos!L54</f>
+        <v>139500</v>
       </c>
       <c r="G55" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11906,22 +11472,28 @@
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
+        <f>Reto1_Datos!A55</f>
         <v>38</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>156</v>
+      <c r="B56" s="7" t="str">
+        <f>Reto1_Datos!B55</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C56" s="7" t="str">
+        <f>Reto1_Datos!C55</f>
+        <v>T1</v>
+      </c>
+      <c r="D56" s="7" t="str">
+        <f>Reto1_Datos!D55</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E56" s="7" t="str">
+        <f>Reto1_Datos!E55</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F56" s="11">
-        <v>216080</v>
+        <f>Reto1_Datos!L55</f>
+        <v>240000</v>
       </c>
       <c r="G56" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11930,22 +11502,28 @@
     </row>
     <row r="57" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
+        <f>Reto1_Datos!A56</f>
         <v>39</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>159</v>
+      <c r="B57" s="7" t="str">
+        <f>Reto1_Datos!B56</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C57" s="7" t="str">
+        <f>Reto1_Datos!C56</f>
+        <v>T1</v>
+      </c>
+      <c r="D57" s="7" t="str">
+        <f>Reto1_Datos!D56</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E57" s="7" t="str">
+        <f>Reto1_Datos!E56</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F57" s="11">
-        <v>355395</v>
+        <f>Reto1_Datos!L56</f>
+        <v>335400</v>
       </c>
       <c r="G57" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11954,22 +11532,28 @@
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
+        <f>Reto1_Datos!A57</f>
         <v>40</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>162</v>
+      <c r="B58" s="7" t="str">
+        <f>Reto1_Datos!B57</f>
+        <v>Abril</v>
+      </c>
+      <c r="C58" s="7" t="str">
+        <f>Reto1_Datos!C57</f>
+        <v>T2</v>
+      </c>
+      <c r="D58" s="7" t="str">
+        <f>Reto1_Datos!D57</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E58" s="7" t="str">
+        <f>Reto1_Datos!E57</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F58" s="11">
-        <v>150615</v>
+        <f>Reto1_Datos!L57</f>
+        <v>144000</v>
       </c>
       <c r="G58" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11978,22 +11562,28 @@
     </row>
     <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
+        <f>Reto1_Datos!A58</f>
         <v>41</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>133</v>
+      <c r="B59" s="7" t="str">
+        <f>Reto1_Datos!B58</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C59" s="7" t="str">
+        <f>Reto1_Datos!C58</f>
+        <v>T2</v>
+      </c>
+      <c r="D59" s="7" t="str">
+        <f>Reto1_Datos!D58</f>
+        <v>Central</v>
+      </c>
+      <c r="E59" s="7" t="str">
+        <f>Reto1_Datos!E58</f>
+        <v>Juan Mora</v>
       </c>
       <c r="F59" s="11">
-        <v>467821</v>
+        <f>Reto1_Datos!L58</f>
+        <v>465000</v>
       </c>
       <c r="G59" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12002,22 +11592,28 @@
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
+        <f>Reto1_Datos!A59</f>
         <v>42</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>167</v>
+      <c r="B60" s="7" t="str">
+        <f>Reto1_Datos!B59</f>
+        <v>Junio</v>
+      </c>
+      <c r="C60" s="7" t="str">
+        <f>Reto1_Datos!C59</f>
+        <v>T2</v>
+      </c>
+      <c r="D60" s="7" t="str">
+        <f>Reto1_Datos!D59</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E60" s="7" t="str">
+        <f>Reto1_Datos!E59</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F60" s="11">
-        <v>17070</v>
+        <f>Reto1_Datos!L59</f>
+        <v>16000</v>
       </c>
       <c r="G60" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12026,22 +11622,28 @@
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
+        <f>Reto1_Datos!A60</f>
         <v>43</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>168</v>
+      <c r="B61" s="7" t="str">
+        <f>Reto1_Datos!B60</f>
+        <v>Julio</v>
+      </c>
+      <c r="C61" s="7" t="str">
+        <f>Reto1_Datos!C60</f>
+        <v>T3</v>
+      </c>
+      <c r="D61" s="7" t="str">
+        <f>Reto1_Datos!D60</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E61" s="7" t="str">
+        <f>Reto1_Datos!E60</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F61" s="11">
-        <v>94188</v>
+        <f>Reto1_Datos!L60</f>
+        <v>102000</v>
       </c>
       <c r="G61" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12050,22 +11652,28 @@
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
+        <f>Reto1_Datos!A61</f>
         <v>44</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>170</v>
+      <c r="B62" s="7" t="str">
+        <f>Reto1_Datos!B61</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C62" s="7" t="str">
+        <f>Reto1_Datos!C61</f>
+        <v>T3</v>
+      </c>
+      <c r="D62" s="7" t="str">
+        <f>Reto1_Datos!D61</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E62" s="7" t="str">
+        <f>Reto1_Datos!E61</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F62" s="11">
-        <v>131688</v>
+        <f>Reto1_Datos!L61</f>
+        <v>130200</v>
       </c>
       <c r="G62" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12074,22 +11682,28 @@
     </row>
     <row r="63" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
+        <f>Reto1_Datos!A62</f>
         <v>45</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>148</v>
+      <c r="B63" s="7" t="str">
+        <f>Reto1_Datos!B62</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C63" s="7" t="str">
+        <f>Reto1_Datos!C62</f>
+        <v>T3</v>
+      </c>
+      <c r="D63" s="7" t="str">
+        <f>Reto1_Datos!D62</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E63" s="7" t="str">
+        <f>Reto1_Datos!E62</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F63" s="11">
-        <v>822</v>
+        <f>Reto1_Datos!L62</f>
+        <v>900</v>
       </c>
       <c r="G63" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12098,22 +11712,28 @@
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
+        <f>Reto1_Datos!A63</f>
         <v>46</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>150</v>
+      <c r="B64" s="7" t="str">
+        <f>Reto1_Datos!B63</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C64" s="7" t="str">
+        <f>Reto1_Datos!C63</f>
+        <v>T4</v>
+      </c>
+      <c r="D64" s="7" t="str">
+        <f>Reto1_Datos!D63</f>
+        <v>Central</v>
+      </c>
+      <c r="E64" s="7" t="str">
+        <f>Reto1_Datos!E63</f>
+        <v>Ana Vargas</v>
       </c>
       <c r="F64" s="11">
-        <v>88184</v>
+        <f>Reto1_Datos!L63</f>
+        <v>96000</v>
       </c>
       <c r="G64" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12122,22 +11742,28 @@
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
+        <f>Reto1_Datos!A64</f>
         <v>47</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>137</v>
+      <c r="B65" s="7" t="str">
+        <f>Reto1_Datos!B64</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C65" s="7" t="str">
+        <f>Reto1_Datos!C64</f>
+        <v>T4</v>
+      </c>
+      <c r="D65" s="7" t="str">
+        <f>Reto1_Datos!D64</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E65" s="7" t="str">
+        <f>Reto1_Datos!E64</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F65" s="11">
-        <v>83304</v>
+        <f>Reto1_Datos!L64</f>
+        <v>81000</v>
       </c>
       <c r="G65" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12146,22 +11772,28 @@
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
+        <f>Reto1_Datos!A65</f>
         <v>48</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>140</v>
+      <c r="B66" s="7" t="str">
+        <f>Reto1_Datos!B65</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <f>Reto1_Datos!C65</f>
+        <v>T4</v>
+      </c>
+      <c r="D66" s="7" t="str">
+        <f>Reto1_Datos!D65</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E66" s="7" t="str">
+        <f>Reto1_Datos!E65</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F66" s="11">
-        <v>362472</v>
+        <f>Reto1_Datos!L65</f>
+        <v>343200</v>
       </c>
       <c r="G66" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12170,22 +11802,28 @@
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
+        <f>Reto1_Datos!A66</f>
         <v>49</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>144</v>
+      <c r="B67" s="7" t="str">
+        <f>Reto1_Datos!B66</f>
+        <v>Enero</v>
+      </c>
+      <c r="C67" s="7" t="str">
+        <f>Reto1_Datos!C66</f>
+        <v>T1</v>
+      </c>
+      <c r="D67" s="7" t="str">
+        <f>Reto1_Datos!D66</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E67" s="7" t="str">
+        <f>Reto1_Datos!E66</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F67" s="11">
-        <v>33968</v>
+        <f>Reto1_Datos!L66</f>
+        <v>37400</v>
       </c>
       <c r="G67" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12194,22 +11832,28 @@
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
+        <f>Reto1_Datos!A67</f>
         <v>50</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>162</v>
+      <c r="B68" s="7" t="str">
+        <f>Reto1_Datos!B67</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C68" s="7" t="str">
+        <f>Reto1_Datos!C67</f>
+        <v>T1</v>
+      </c>
+      <c r="D68" s="7" t="str">
+        <f>Reto1_Datos!D67</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E68" s="7" t="str">
+        <f>Reto1_Datos!E67</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F68" s="11">
-        <v>15489</v>
+        <f>Reto1_Datos!L67</f>
+        <v>16500</v>
       </c>
       <c r="G68" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12218,22 +11862,28 @@
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
+        <f>Reto1_Datos!A68</f>
         <v>51</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>165</v>
+      <c r="B69" s="7" t="str">
+        <f>Reto1_Datos!B68</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C69" s="7" t="str">
+        <f>Reto1_Datos!C68</f>
+        <v>T1</v>
+      </c>
+      <c r="D69" s="7" t="str">
+        <f>Reto1_Datos!D68</f>
+        <v>Central</v>
+      </c>
+      <c r="E69" s="7" t="str">
+        <f>Reto1_Datos!E68</f>
+        <v>Carlos Solano</v>
       </c>
       <c r="F69" s="11">
-        <v>108936</v>
+        <f>Reto1_Datos!L68</f>
+        <v>108800</v>
       </c>
       <c r="G69" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12242,22 +11892,28 @@
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
+        <f>Reto1_Datos!A69</f>
         <v>52</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>153</v>
+      <c r="B70" s="7" t="str">
+        <f>Reto1_Datos!B69</f>
+        <v>Abril</v>
+      </c>
+      <c r="C70" s="7" t="str">
+        <f>Reto1_Datos!C69</f>
+        <v>T2</v>
+      </c>
+      <c r="D70" s="7" t="str">
+        <f>Reto1_Datos!D69</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E70" s="7" t="str">
+        <f>Reto1_Datos!E69</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F70" s="11">
-        <v>52152</v>
+        <f>Reto1_Datos!L69</f>
+        <v>56000</v>
       </c>
       <c r="G70" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12266,22 +11922,28 @@
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
+        <f>Reto1_Datos!A70</f>
         <v>53</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>156</v>
+      <c r="B71" s="7" t="str">
+        <f>Reto1_Datos!B70</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C71" s="7" t="str">
+        <f>Reto1_Datos!C70</f>
+        <v>T2</v>
+      </c>
+      <c r="D71" s="7" t="str">
+        <f>Reto1_Datos!D70</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E71" s="7" t="str">
+        <f>Reto1_Datos!E70</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F71" s="11">
-        <v>2999964</v>
+        <f>Reto1_Datos!L70</f>
+        <v>2860000</v>
       </c>
       <c r="G71" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12290,22 +11952,28 @@
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
+        <f>Reto1_Datos!A71</f>
         <v>54</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>159</v>
+      <c r="B72" s="7" t="str">
+        <f>Reto1_Datos!B71</f>
+        <v>Junio</v>
+      </c>
+      <c r="C72" s="7" t="str">
+        <f>Reto1_Datos!C71</f>
+        <v>T2</v>
+      </c>
+      <c r="D72" s="7" t="str">
+        <f>Reto1_Datos!D71</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E72" s="7" t="str">
+        <f>Reto1_Datos!E71</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F72" s="11">
-        <v>30190</v>
+        <f>Reto1_Datos!L71</f>
+        <v>28000</v>
       </c>
       <c r="G72" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12314,22 +11982,28 @@
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
+        <f>Reto1_Datos!A72</f>
         <v>55</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>148</v>
+      <c r="B73" s="7" t="str">
+        <f>Reto1_Datos!B72</f>
+        <v>Julio</v>
+      </c>
+      <c r="C73" s="7" t="str">
+        <f>Reto1_Datos!C72</f>
+        <v>T3</v>
+      </c>
+      <c r="D73" s="7" t="str">
+        <f>Reto1_Datos!D72</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E73" s="7" t="str">
+        <f>Reto1_Datos!E72</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F73" s="11">
-        <v>35410</v>
+        <f>Reto1_Datos!L72</f>
+        <v>36000</v>
       </c>
       <c r="G73" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12338,22 +12012,28 @@
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
+        <f>Reto1_Datos!A73</f>
         <v>56</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>172</v>
+      <c r="B74" s="7" t="str">
+        <f>Reto1_Datos!B73</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C74" s="7" t="str">
+        <f>Reto1_Datos!C73</f>
+        <v>T3</v>
+      </c>
+      <c r="D74" s="7" t="str">
+        <f>Reto1_Datos!D73</f>
+        <v>Central</v>
+      </c>
+      <c r="E74" s="7" t="str">
+        <f>Reto1_Datos!E73</f>
+        <v>Rita Ulate</v>
       </c>
       <c r="F74" s="11">
-        <v>66472</v>
+        <f>Reto1_Datos!L73</f>
+        <v>68000</v>
       </c>
       <c r="G74" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12362,22 +12042,28 @@
     </row>
     <row r="75" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
+        <f>Reto1_Datos!A74</f>
         <v>57</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>167</v>
+      <c r="B75" s="7" t="str">
+        <f>Reto1_Datos!B74</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C75" s="7" t="str">
+        <f>Reto1_Datos!C74</f>
+        <v>T3</v>
+      </c>
+      <c r="D75" s="7" t="str">
+        <f>Reto1_Datos!D74</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E75" s="7" t="str">
+        <f>Reto1_Datos!E74</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F75" s="11">
-        <v>139350</v>
+        <f>Reto1_Datos!L74</f>
+        <v>147000</v>
       </c>
       <c r="G75" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12386,22 +12072,28 @@
     </row>
     <row r="76" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
+        <f>Reto1_Datos!A75</f>
         <v>58</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>168</v>
+      <c r="B76" s="7" t="str">
+        <f>Reto1_Datos!B75</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C76" s="7" t="str">
+        <f>Reto1_Datos!C75</f>
+        <v>T4</v>
+      </c>
+      <c r="D76" s="7" t="str">
+        <f>Reto1_Datos!D75</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E76" s="7" t="str">
+        <f>Reto1_Datos!E75</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F76" s="11">
-        <v>51488</v>
+        <f>Reto1_Datos!L75</f>
+        <v>56000</v>
       </c>
       <c r="G76" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12410,22 +12102,28 @@
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
+        <f>Reto1_Datos!A76</f>
         <v>59</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>170</v>
+      <c r="B77" s="7" t="str">
+        <f>Reto1_Datos!B76</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C77" s="7" t="str">
+        <f>Reto1_Datos!C76</f>
+        <v>T4</v>
+      </c>
+      <c r="D77" s="7" t="str">
+        <f>Reto1_Datos!D76</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E77" s="7" t="str">
+        <f>Reto1_Datos!E76</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F77" s="11">
-        <v>9600</v>
+        <f>Reto1_Datos!L76</f>
+        <v>9500</v>
       </c>
       <c r="G77" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12434,22 +12132,28 @@
     </row>
     <row r="78" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
+        <f>Reto1_Datos!A77</f>
         <v>60</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>162</v>
+      <c r="B78" s="7" t="str">
+        <f>Reto1_Datos!B77</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C78" s="7" t="str">
+        <f>Reto1_Datos!C77</f>
+        <v>T4</v>
+      </c>
+      <c r="D78" s="7" t="str">
+        <f>Reto1_Datos!D77</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E78" s="7" t="str">
+        <f>Reto1_Datos!E77</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F78" s="11">
-        <v>3910</v>
+        <f>Reto1_Datos!L77</f>
+        <v>3800</v>
       </c>
       <c r="G78" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12458,22 +12162,28 @@
     </row>
     <row r="79" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
+        <f>Reto1_Datos!A78</f>
         <v>61</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>133</v>
+      <c r="B79" s="7" t="str">
+        <f>Reto1_Datos!B78</f>
+        <v>Enero</v>
+      </c>
+      <c r="C79" s="7" t="str">
+        <f>Reto1_Datos!C78</f>
+        <v>T1</v>
+      </c>
+      <c r="D79" s="7" t="str">
+        <f>Reto1_Datos!D78</f>
+        <v>Central</v>
+      </c>
+      <c r="E79" s="7" t="str">
+        <f>Reto1_Datos!E78</f>
+        <v>Juan Mora</v>
       </c>
       <c r="F79" s="11">
-        <v>25410</v>
+        <f>Reto1_Datos!L78</f>
+        <v>25500</v>
       </c>
       <c r="G79" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12482,22 +12192,28 @@
     </row>
     <row r="80" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
+        <f>Reto1_Datos!A79</f>
         <v>62</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>137</v>
+      <c r="B80" s="7" t="str">
+        <f>Reto1_Datos!B79</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C80" s="7" t="str">
+        <f>Reto1_Datos!C79</f>
+        <v>T1</v>
+      </c>
+      <c r="D80" s="7" t="str">
+        <f>Reto1_Datos!D79</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E80" s="7" t="str">
+        <f>Reto1_Datos!E79</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F80" s="11">
-        <v>146276</v>
+        <f>Reto1_Datos!L79</f>
+        <v>156000</v>
       </c>
       <c r="G80" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12506,22 +12222,28 @@
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
+        <f>Reto1_Datos!A80</f>
         <v>63</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>140</v>
+      <c r="B81" s="7" t="str">
+        <f>Reto1_Datos!B80</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C81" s="7" t="str">
+        <f>Reto1_Datos!C80</f>
+        <v>T1</v>
+      </c>
+      <c r="D81" s="7" t="str">
+        <f>Reto1_Datos!D80</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E81" s="7" t="str">
+        <f>Reto1_Datos!E80</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F81" s="11">
-        <v>1818642</v>
+        <f>Reto1_Datos!L80</f>
+        <v>1890000</v>
       </c>
       <c r="G81" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12530,22 +12252,28 @@
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
+        <f>Reto1_Datos!A81</f>
         <v>64</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>144</v>
+      <c r="B82" s="7" t="str">
+        <f>Reto1_Datos!B81</f>
+        <v>Abril</v>
+      </c>
+      <c r="C82" s="7" t="str">
+        <f>Reto1_Datos!C81</f>
+        <v>T2</v>
+      </c>
+      <c r="D82" s="7" t="str">
+        <f>Reto1_Datos!D81</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E82" s="7" t="str">
+        <f>Reto1_Datos!E81</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F82" s="11">
-        <v>328856</v>
+        <f>Reto1_Datos!L81</f>
+        <v>304000</v>
       </c>
       <c r="G82" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12554,22 +12282,28 @@
     </row>
     <row r="83" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
+        <f>Reto1_Datos!A82</f>
         <v>65</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>148</v>
+      <c r="B83" s="7" t="str">
+        <f>Reto1_Datos!B82</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C83" s="7" t="str">
+        <f>Reto1_Datos!C82</f>
+        <v>T2</v>
+      </c>
+      <c r="D83" s="7" t="str">
+        <f>Reto1_Datos!D82</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E83" s="7" t="str">
+        <f>Reto1_Datos!E82</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F83" s="11">
-        <v>160020</v>
+        <f>Reto1_Datos!L82</f>
+        <v>170000</v>
       </c>
       <c r="G83" s="4" t="str">
         <f t="shared" ref="G83:G114" si="2">IF(F83&gt;=500000,"Premium",IF(F83&gt;=200000,"Regular","Basico"))</f>
@@ -12578,22 +12312,28 @@
     </row>
     <row r="84" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
+        <f>Reto1_Datos!A83</f>
         <v>66</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>150</v>
+      <c r="B84" s="7" t="str">
+        <f>Reto1_Datos!B83</f>
+        <v>Junio</v>
+      </c>
+      <c r="C84" s="7" t="str">
+        <f>Reto1_Datos!C83</f>
+        <v>T2</v>
+      </c>
+      <c r="D84" s="7" t="str">
+        <f>Reto1_Datos!D83</f>
+        <v>Central</v>
+      </c>
+      <c r="E84" s="7" t="str">
+        <f>Reto1_Datos!E83</f>
+        <v>Ana Vargas</v>
       </c>
       <c r="F84" s="11">
-        <v>177038</v>
+        <f>Reto1_Datos!L83</f>
+        <v>184500</v>
       </c>
       <c r="G84" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12602,22 +12342,28 @@
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
+        <f>Reto1_Datos!A84</f>
         <v>67</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>153</v>
+      <c r="B85" s="7" t="str">
+        <f>Reto1_Datos!B84</f>
+        <v>Julio</v>
+      </c>
+      <c r="C85" s="7" t="str">
+        <f>Reto1_Datos!C84</f>
+        <v>T3</v>
+      </c>
+      <c r="D85" s="7" t="str">
+        <f>Reto1_Datos!D84</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E85" s="7" t="str">
+        <f>Reto1_Datos!E84</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F85" s="11">
-        <v>728955</v>
+        <f>Reto1_Datos!L84</f>
+        <v>697500</v>
       </c>
       <c r="G85" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12626,22 +12372,28 @@
     </row>
     <row r="86" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
+        <f>Reto1_Datos!A85</f>
         <v>68</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>156</v>
+      <c r="B86" s="7" t="str">
+        <f>Reto1_Datos!B85</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C86" s="7" t="str">
+        <f>Reto1_Datos!C85</f>
+        <v>T3</v>
+      </c>
+      <c r="D86" s="7" t="str">
+        <f>Reto1_Datos!D85</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E86" s="7" t="str">
+        <f>Reto1_Datos!E85</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F86" s="11">
-        <v>22924</v>
+        <f>Reto1_Datos!L85</f>
+        <v>24000</v>
       </c>
       <c r="G86" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12650,46 +12402,58 @@
     </row>
     <row r="87" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
+        <f>Reto1_Datos!A86</f>
         <v>69</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>159</v>
+      <c r="B87" s="7" t="str">
+        <f>Reto1_Datos!B86</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C87" s="7" t="str">
+        <f>Reto1_Datos!C86</f>
+        <v>T3</v>
+      </c>
+      <c r="D87" s="7" t="str">
+        <f>Reto1_Datos!D86</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E87" s="7" t="str">
+        <f>Reto1_Datos!E86</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F87" s="11">
-        <v>197652</v>
+        <f>Reto1_Datos!L86</f>
+        <v>202800</v>
       </c>
       <c r="G87" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>Basico</v>
+        <v>Regular</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
+        <f>Reto1_Datos!A87</f>
         <v>70</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>162</v>
+      <c r="B88" s="7" t="str">
+        <f>Reto1_Datos!B87</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C88" s="7" t="str">
+        <f>Reto1_Datos!C87</f>
+        <v>T4</v>
+      </c>
+      <c r="D88" s="7" t="str">
+        <f>Reto1_Datos!D87</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E88" s="7" t="str">
+        <f>Reto1_Datos!E87</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F88" s="11">
-        <v>62660</v>
+        <f>Reto1_Datos!L87</f>
+        <v>64000</v>
       </c>
       <c r="G88" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12698,22 +12462,28 @@
     </row>
     <row r="89" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
+        <f>Reto1_Datos!A88</f>
         <v>71</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>165</v>
+      <c r="B89" s="7" t="str">
+        <f>Reto1_Datos!B88</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C89" s="7" t="str">
+        <f>Reto1_Datos!C88</f>
+        <v>T4</v>
+      </c>
+      <c r="D89" s="7" t="str">
+        <f>Reto1_Datos!D88</f>
+        <v>Central</v>
+      </c>
+      <c r="E89" s="7" t="str">
+        <f>Reto1_Datos!E88</f>
+        <v>Carlos Solano</v>
       </c>
       <c r="F89" s="11">
-        <v>493830</v>
+        <f>Reto1_Datos!L88</f>
+        <v>465000</v>
       </c>
       <c r="G89" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12722,22 +12492,28 @@
     </row>
     <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
+        <f>Reto1_Datos!A89</f>
         <v>72</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>167</v>
+      <c r="B90" s="7" t="str">
+        <f>Reto1_Datos!B89</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C90" s="7" t="str">
+        <f>Reto1_Datos!C89</f>
+        <v>T4</v>
+      </c>
+      <c r="D90" s="7" t="str">
+        <f>Reto1_Datos!D89</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E90" s="7" t="str">
+        <f>Reto1_Datos!E89</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F90" s="11">
-        <v>19494</v>
+        <f>Reto1_Datos!L89</f>
+        <v>19200</v>
       </c>
       <c r="G90" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12746,22 +12522,28 @@
     </row>
     <row r="91" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
+        <f>Reto1_Datos!A90</f>
         <v>73</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>168</v>
+      <c r="B91" s="7" t="str">
+        <f>Reto1_Datos!B90</f>
+        <v>Enero</v>
+      </c>
+      <c r="C91" s="7" t="str">
+        <f>Reto1_Datos!C90</f>
+        <v>T1</v>
+      </c>
+      <c r="D91" s="7" t="str">
+        <f>Reto1_Datos!D90</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E91" s="7" t="str">
+        <f>Reto1_Datos!E90</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F91" s="11">
-        <v>139335</v>
+        <f>Reto1_Datos!L90</f>
+        <v>127500</v>
       </c>
       <c r="G91" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12770,22 +12552,28 @@
     </row>
     <row r="92" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
+        <f>Reto1_Datos!A91</f>
         <v>74</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>170</v>
+      <c r="B92" s="7" t="str">
+        <f>Reto1_Datos!B91</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C92" s="7" t="str">
+        <f>Reto1_Datos!C91</f>
+        <v>T1</v>
+      </c>
+      <c r="D92" s="7" t="str">
+        <f>Reto1_Datos!D91</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E92" s="7" t="str">
+        <f>Reto1_Datos!E91</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F92" s="11">
-        <v>8736</v>
+        <f>Reto1_Datos!L91</f>
+        <v>8400</v>
       </c>
       <c r="G92" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12794,22 +12582,28 @@
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
+        <f>Reto1_Datos!A92</f>
         <v>75</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>148</v>
+      <c r="B93" s="7" t="str">
+        <f>Reto1_Datos!B92</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C93" s="7" t="str">
+        <f>Reto1_Datos!C92</f>
+        <v>T1</v>
+      </c>
+      <c r="D93" s="7" t="str">
+        <f>Reto1_Datos!D92</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E93" s="7" t="str">
+        <f>Reto1_Datos!E92</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F93" s="11">
-        <v>14385</v>
+        <f>Reto1_Datos!L92</f>
+        <v>15750</v>
       </c>
       <c r="G93" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12818,22 +12612,28 @@
     </row>
     <row r="94" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
+        <f>Reto1_Datos!A93</f>
         <v>76</v>
       </c>
-      <c r="B94" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>172</v>
+      <c r="B94" s="7" t="str">
+        <f>Reto1_Datos!B93</f>
+        <v>Abril</v>
+      </c>
+      <c r="C94" s="7" t="str">
+        <f>Reto1_Datos!C93</f>
+        <v>T2</v>
+      </c>
+      <c r="D94" s="7" t="str">
+        <f>Reto1_Datos!D93</f>
+        <v>Central</v>
+      </c>
+      <c r="E94" s="7" t="str">
+        <f>Reto1_Datos!E93</f>
+        <v>Rita Ulate</v>
       </c>
       <c r="F94" s="11">
-        <v>454841</v>
+        <f>Reto1_Datos!L93</f>
+        <v>444000</v>
       </c>
       <c r="G94" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12842,22 +12642,28 @@
     </row>
     <row r="95" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
+        <f>Reto1_Datos!A94</f>
         <v>77</v>
       </c>
-      <c r="B95" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>137</v>
+      <c r="B95" s="7" t="str">
+        <f>Reto1_Datos!B94</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C95" s="7" t="str">
+        <f>Reto1_Datos!C94</f>
+        <v>T2</v>
+      </c>
+      <c r="D95" s="7" t="str">
+        <f>Reto1_Datos!D94</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E95" s="7" t="str">
+        <f>Reto1_Datos!E94</f>
+        <v>Luis Brenes</v>
       </c>
       <c r="F95" s="11">
-        <v>107939</v>
+        <f>Reto1_Datos!L94</f>
+        <v>103500</v>
       </c>
       <c r="G95" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12866,22 +12672,28 @@
     </row>
     <row r="96" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
+        <f>Reto1_Datos!A95</f>
         <v>78</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>140</v>
+      <c r="B96" s="7" t="str">
+        <f>Reto1_Datos!B95</f>
+        <v>Junio</v>
+      </c>
+      <c r="C96" s="7" t="str">
+        <f>Reto1_Datos!C95</f>
+        <v>T2</v>
+      </c>
+      <c r="D96" s="7" t="str">
+        <f>Reto1_Datos!D95</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E96" s="7" t="str">
+        <f>Reto1_Datos!E95</f>
+        <v>Fabiola Rios</v>
       </c>
       <c r="F96" s="11">
-        <v>96889</v>
+        <f>Reto1_Datos!L95</f>
+        <v>101400</v>
       </c>
       <c r="G96" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12890,22 +12702,28 @@
     </row>
     <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
+        <f>Reto1_Datos!A96</f>
         <v>79</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>144</v>
+      <c r="B97" s="7" t="str">
+        <f>Reto1_Datos!B96</f>
+        <v>Julio</v>
+      </c>
+      <c r="C97" s="7" t="str">
+        <f>Reto1_Datos!C96</f>
+        <v>T3</v>
+      </c>
+      <c r="D97" s="7" t="str">
+        <f>Reto1_Datos!D96</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E97" s="7" t="str">
+        <f>Reto1_Datos!E96</f>
+        <v>Rosa Mendez</v>
       </c>
       <c r="F97" s="11">
-        <v>36320</v>
+        <f>Reto1_Datos!L96</f>
+        <v>34000</v>
       </c>
       <c r="G97" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12914,22 +12732,28 @@
     </row>
     <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
+        <f>Reto1_Datos!A97</f>
         <v>80</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>162</v>
+      <c r="B98" s="7" t="str">
+        <f>Reto1_Datos!B97</f>
+        <v>Agosto</v>
+      </c>
+      <c r="C98" s="7" t="str">
+        <f>Reto1_Datos!C97</f>
+        <v>T3</v>
+      </c>
+      <c r="D98" s="7" t="str">
+        <f>Reto1_Datos!D97</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E98" s="7" t="str">
+        <f>Reto1_Datos!E97</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F98" s="11">
-        <v>39616</v>
+        <f>Reto1_Datos!L97</f>
+        <v>44000</v>
       </c>
       <c r="G98" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12938,22 +12762,28 @@
     </row>
     <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
+        <f>Reto1_Datos!A98</f>
         <v>81</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>133</v>
+      <c r="B99" s="7" t="str">
+        <f>Reto1_Datos!B98</f>
+        <v>Septiembre</v>
+      </c>
+      <c r="C99" s="7" t="str">
+        <f>Reto1_Datos!C98</f>
+        <v>T3</v>
+      </c>
+      <c r="D99" s="7" t="str">
+        <f>Reto1_Datos!D98</f>
+        <v>Central</v>
+      </c>
+      <c r="E99" s="7" t="str">
+        <f>Reto1_Datos!E98</f>
+        <v>Juan Mora</v>
       </c>
       <c r="F99" s="11">
-        <v>12060</v>
+        <f>Reto1_Datos!L98</f>
+        <v>12800</v>
       </c>
       <c r="G99" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12962,22 +12792,28 @@
     </row>
     <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
+        <f>Reto1_Datos!A99</f>
         <v>82</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>153</v>
+      <c r="B100" s="7" t="str">
+        <f>Reto1_Datos!B99</f>
+        <v>Octubre</v>
+      </c>
+      <c r="C100" s="7" t="str">
+        <f>Reto1_Datos!C99</f>
+        <v>T4</v>
+      </c>
+      <c r="D100" s="7" t="str">
+        <f>Reto1_Datos!D99</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E100" s="7" t="str">
+        <f>Reto1_Datos!E99</f>
+        <v>Maria Jimenez</v>
       </c>
       <c r="F100" s="11">
-        <v>429930</v>
+        <f>Reto1_Datos!L99</f>
+        <v>420000</v>
       </c>
       <c r="G100" s="4" t="str">
         <f t="shared" si="2"/>
@@ -12986,22 +12822,28 @@
     </row>
     <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
+        <f>Reto1_Datos!A100</f>
         <v>83</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>156</v>
+      <c r="B101" s="7" t="str">
+        <f>Reto1_Datos!B100</f>
+        <v>Noviembre</v>
+      </c>
+      <c r="C101" s="7" t="str">
+        <f>Reto1_Datos!C100</f>
+        <v>T4</v>
+      </c>
+      <c r="D101" s="7" t="str">
+        <f>Reto1_Datos!D100</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E101" s="7" t="str">
+        <f>Reto1_Datos!E100</f>
+        <v>Pedro Quesada</v>
       </c>
       <c r="F101" s="11">
-        <v>1821177</v>
+        <f>Reto1_Datos!L100</f>
+        <v>1755000</v>
       </c>
       <c r="G101" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13010,22 +12852,28 @@
     </row>
     <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
+        <f>Reto1_Datos!A101</f>
         <v>84</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>159</v>
+      <c r="B102" s="7" t="str">
+        <f>Reto1_Datos!B101</f>
+        <v>Diciembre</v>
+      </c>
+      <c r="C102" s="7" t="str">
+        <f>Reto1_Datos!C101</f>
+        <v>T4</v>
+      </c>
+      <c r="D102" s="7" t="str">
+        <f>Reto1_Datos!D101</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E102" s="7" t="str">
+        <f>Reto1_Datos!E101</f>
+        <v>Patricia Salas</v>
       </c>
       <c r="F102" s="11">
-        <v>19922</v>
+        <f>Reto1_Datos!L101</f>
+        <v>19600</v>
       </c>
       <c r="G102" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13034,22 +12882,28 @@
     </row>
     <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
+        <f>Reto1_Datos!A102</f>
         <v>85</v>
       </c>
-      <c r="B103" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>148</v>
+      <c r="B103" s="7" t="str">
+        <f>Reto1_Datos!B102</f>
+        <v>Enero</v>
+      </c>
+      <c r="C103" s="7" t="str">
+        <f>Reto1_Datos!C102</f>
+        <v>T1</v>
+      </c>
+      <c r="D103" s="7" t="str">
+        <f>Reto1_Datos!D102</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E103" s="7" t="str">
+        <f>Reto1_Datos!E102</f>
+        <v>Andres Mora</v>
       </c>
       <c r="F103" s="11">
-        <v>95200</v>
+        <f>Reto1_Datos!L102</f>
+        <v>90000</v>
       </c>
       <c r="G103" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13058,22 +12912,28 @@
     </row>
     <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
+        <f>Reto1_Datos!A103</f>
         <v>86</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>150</v>
+      <c r="B104" s="7" t="str">
+        <f>Reto1_Datos!B103</f>
+        <v>Febrero</v>
+      </c>
+      <c r="C104" s="7" t="str">
+        <f>Reto1_Datos!C103</f>
+        <v>T1</v>
+      </c>
+      <c r="D104" s="7" t="str">
+        <f>Reto1_Datos!D103</f>
+        <v>Central</v>
+      </c>
+      <c r="E104" s="7" t="str">
+        <f>Reto1_Datos!E103</f>
+        <v>Ana Vargas</v>
       </c>
       <c r="F104" s="11">
-        <v>232020</v>
+        <f>Reto1_Datos!L103</f>
+        <v>255000</v>
       </c>
       <c r="G104" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13082,22 +12942,28 @@
     </row>
     <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
+        <f>Reto1_Datos!A104</f>
         <v>87</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>167</v>
+      <c r="B105" s="7" t="str">
+        <f>Reto1_Datos!B104</f>
+        <v>Marzo</v>
+      </c>
+      <c r="C105" s="7" t="str">
+        <f>Reto1_Datos!C104</f>
+        <v>T1</v>
+      </c>
+      <c r="D105" s="7" t="str">
+        <f>Reto1_Datos!D104</f>
+        <v>Cartago</v>
+      </c>
+      <c r="E105" s="7" t="str">
+        <f>Reto1_Datos!E104</f>
+        <v>Sandra Vega</v>
       </c>
       <c r="F105" s="11">
-        <v>390827</v>
+        <f>Reto1_Datos!L104</f>
+        <v>421400</v>
       </c>
       <c r="G105" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13106,22 +12972,28 @@
     </row>
     <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
+        <f>Reto1_Datos!A105</f>
         <v>88</v>
       </c>
-      <c r="B106" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>168</v>
+      <c r="B106" s="7" t="str">
+        <f>Reto1_Datos!B105</f>
+        <v>Abril</v>
+      </c>
+      <c r="C106" s="7" t="str">
+        <f>Reto1_Datos!C105</f>
+        <v>T2</v>
+      </c>
+      <c r="D106" s="7" t="str">
+        <f>Reto1_Datos!D105</f>
+        <v>Heredia</v>
+      </c>
+      <c r="E106" s="7" t="str">
+        <f>Reto1_Datos!E105</f>
+        <v>Diana Castro</v>
       </c>
       <c r="F106" s="11">
-        <v>139933</v>
+        <f>Reto1_Datos!L105</f>
+        <v>143500</v>
       </c>
       <c r="G106" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13130,22 +13002,28 @@
     </row>
     <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
+        <f>Reto1_Datos!A106</f>
         <v>89</v>
       </c>
-      <c r="B107" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>170</v>
+      <c r="B107" s="7" t="str">
+        <f>Reto1_Datos!B106</f>
+        <v>Mayo</v>
+      </c>
+      <c r="C107" s="7" t="str">
+        <f>Reto1_Datos!C106</f>
+        <v>T2</v>
+      </c>
+      <c r="D107" s="7" t="str">
+        <f>Reto1_Datos!D106</f>
+        <v>Alajuela</v>
+      </c>
+      <c r="E107" s="7" t="str">
+        <f>Reto1_Datos!E106</f>
+        <v>Fabio Ulate</v>
       </c>
       <c r="F107" s="11">
-        <v>34410</v>
+        <f>Reto1_Datos!L106</f>
+        <v>35150</v>
       </c>
       <c r="G107" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13154,22 +13032,28 @@
     </row>
     <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
+        <f>Reto1_Datos!A107</f>
         <v>90</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>162</v>
+      <c r="B108" s="7" t="str">
+        <f>Reto1_Datos!B107</f>
+        <v>Junio</v>
+      </c>
+      <c r="C108" s="7" t="str">
+        <f>Reto1_Datos!C107</f>
+        <v>T2</v>
+      </c>
+      <c r="D108" s="7" t="str">
+        <f>Reto1_Datos!D107</f>
+        <v>Liberia</v>
+      </c>
+      <c r="E108" s="7" t="str">
+        <f>Reto1_Datos!E107</f>
+        <v>Karina Solis</v>
       </c>
       <c r="F108" s="11">
-        <v>6156</v>
+        <f>Reto1_Datos!L107</f>
+        <v>6840</v>
       </c>
       <c r="G108" s="4" t="str">
         <f t="shared" si="2"/>
@@ -13178,29 +13062,29 @@
     </row>
     <row r="109" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="110" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
-      <c r="D110" s="26"/>
-      <c r="E110" s="26"/>
-      <c r="F110" s="26"/>
-      <c r="G110" s="26"/>
-      <c r="H110" s="27"/>
+      <c r="A110" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="B110" s="30"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="30"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+      <c r="H110" s="31"/>
     </row>
     <row r="111" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>122</v>
       </c>
       <c r="B111" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="D111" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -13208,11 +13092,11 @@
         <v>132</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C112" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A112,$G$19:$G$108,$B112)</f>
-        <v>681450</v>
+        <v>630000</v>
       </c>
       <c r="D112" s="14">
         <f>COUNTIFS($D$19:$D$108,$A112,$G$19:$G$108,$B112)</f>
@@ -13224,11 +13108,11 @@
         <v>132</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C113" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A113,$G$19:$G$108,$B113)</f>
-        <v>2001972</v>
+        <v>1994500</v>
       </c>
       <c r="D113" s="14">
         <f>COUNTIFS($D$19:$D$108,$A113,$G$19:$G$108,$B113)</f>
@@ -13240,11 +13124,11 @@
         <v>132</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C114" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A114,$G$19:$G$108,$B114)</f>
-        <v>710598</v>
+        <v>722300</v>
       </c>
       <c r="D114" s="14">
         <f>COUNTIFS($D$19:$D$108,$A114,$G$19:$G$108,$B114)</f>
@@ -13257,11 +13141,11 @@
         <v>136</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C116" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A116,$G$19:$G$108,$B116)</f>
-        <v>728955</v>
+        <v>697500</v>
       </c>
       <c r="D116" s="14">
         <f>COUNTIFS($D$19:$D$108,$A116,$G$19:$G$108,$B116)</f>
@@ -13273,11 +13157,11 @@
         <v>136</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C117" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A117,$G$19:$G$108,$B117)</f>
-        <v>2054553</v>
+        <v>2051400</v>
       </c>
       <c r="D117" s="14">
         <f>COUNTIFS($D$19:$D$108,$A117,$G$19:$G$108,$B117)</f>
@@ -13289,11 +13173,11 @@
         <v>136</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C118" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A118,$G$19:$G$108,$B118)</f>
-        <v>1024895</v>
+        <v>1048300</v>
       </c>
       <c r="D118" s="14">
         <f>COUNTIFS($D$19:$D$108,$A118,$G$19:$G$108,$B118)</f>
@@ -13306,11 +13190,11 @@
         <v>139</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C120" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A120,$G$19:$G$108,$B120)</f>
-        <v>9326583</v>
+        <v>9115000</v>
       </c>
       <c r="D120" s="14">
         <f>COUNTIFS($D$19:$D$108,$A120,$G$19:$G$108,$B120)</f>
@@ -13322,11 +13206,11 @@
         <v>139</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C121" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A121,$G$19:$G$108,$B121)</f>
-        <v>1134528</v>
+        <v>1172200</v>
       </c>
       <c r="D121" s="14">
         <f>COUNTIFS($D$19:$D$108,$A121,$G$19:$G$108,$B121)</f>
@@ -13338,11 +13222,11 @@
         <v>139</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C122" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A122,$G$19:$G$108,$B122)</f>
-        <v>895998</v>
+        <v>916900</v>
       </c>
       <c r="D122" s="14">
         <f>COUNTIFS($D$19:$D$108,$A122,$G$19:$G$108,$B122)</f>
@@ -13355,11 +13239,11 @@
         <v>143</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C124" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A124,$G$19:$G$108,$B124)</f>
-        <v>1383720</v>
+        <v>1520000</v>
       </c>
       <c r="D124" s="14">
         <f>COUNTIFS($D$19:$D$108,$A124,$G$19:$G$108,$B124)</f>
@@ -13371,15 +13255,15 @@
         <v>143</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C125" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A125,$G$19:$G$108,$B125)</f>
-        <v>1311994</v>
+        <v>1450400</v>
       </c>
       <c r="D125" s="14">
         <f>COUNTIFS($D$19:$D$108,$A125,$G$19:$G$108,$B125)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -13387,15 +13271,15 @@
         <v>143</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C126" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A126,$G$19:$G$108,$B126)</f>
-        <v>801533</v>
+        <v>604100</v>
       </c>
       <c r="D126" s="14">
         <f>COUNTIFS($D$19:$D$108,$A126,$G$19:$G$108,$B126)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -13404,7 +13288,7 @@
         <v>147</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C128" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A128,$G$19:$G$108,$B128)</f>
@@ -13420,11 +13304,11 @@
         <v>147</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C129" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A129,$G$19:$G$108,$B129)</f>
-        <v>349182</v>
+        <v>323000</v>
       </c>
       <c r="D129" s="14">
         <f>COUNTIFS($D$19:$D$108,$A129,$G$19:$G$108,$B129)</f>
@@ -13436,11 +13320,11 @@
         <v>147</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C130" s="14">
         <f>SUMIFS($F$19:$F$108,$D$19:$D$108,$A130,$G$19:$G$108,$B130)</f>
-        <v>881762</v>
+        <v>893700</v>
       </c>
       <c r="D130" s="14">
         <f>COUNTIFS($D$19:$D$108,$A130,$G$19:$G$108,$B130)</f>
@@ -13450,11 +13334,6 @@
     <row r="131" spans="1:4" ht="4" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A110:H110"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:H1"/>
@@ -13462,6 +13341,11 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A9:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13480,26 +13364,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27"/>
+      <c r="A1" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
+      <c r="A2" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13507,22 +13391,22 @@
         <v>122</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -13672,122 +13556,125 @@
     </row>
     <row r="10" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:7" ht="220" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47"/>
+      <c r="A11" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="59"/>
     </row>
     <row r="12" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="27"/>
+      <c r="A13" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="34"/>
+      <c r="A14" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
     </row>
     <row r="15" spans="1:7" ht="77" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="34"/>
+      <c r="A15" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="34"/>
+      <c r="A17" s="60" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" spans="1:7" ht="158" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="44" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="34"/>
+      <c r="A18" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
     </row>
     <row r="19" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="34"/>
+      <c r="A20" s="60" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
     </row>
     <row r="21" spans="1:7" ht="88" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="34"/>
+      <c r="A21" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="34"/>
+      <c r="A23" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
     </row>
     <row r="24" spans="1:7" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="34"/>
+      <c r="A24" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
     </row>
     <row r="25" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A24:G24"/>
@@ -13797,9 +13684,6 @@
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13837,53 +13721,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="27"/>
+      <c r="A1" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="31"/>
       <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:30" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
+      <c r="A2" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="M3" s="22"/>
     </row>
     <row r="4" spans="1:30" ht="140" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47"/>
+      <c r="A4" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13920,21 +13804,21 @@
       <c r="K6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="R6" s="63"/>
-      <c r="S6" s="64" t="s">
-        <v>344</v>
-      </c>
-      <c r="T6" s="63"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="63"/>
-      <c r="W6" s="63"/>
-      <c r="X6" s="63"/>
-      <c r="Y6" s="63"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
     </row>
     <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
@@ -13970,32 +13854,32 @@
       <c r="K7" s="11">
         <v>24210</v>
       </c>
-      <c r="R7" s="63"/>
-      <c r="S7" s="63" t="s">
+      <c r="R7" s="25"/>
+      <c r="S7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="T7" s="63"/>
-      <c r="U7" s="63" t="s">
+      <c r="T7" s="25"/>
+      <c r="U7" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="V7" s="63"/>
-      <c r="W7" s="63" t="s">
+      <c r="V7" s="25"/>
+      <c r="W7" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="X7" s="63"/>
-      <c r="Y7" s="63" t="s">
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Z7" s="63"/>
-      <c r="AA7" s="63" t="s">
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB7" s="63"/>
-      <c r="AC7" s="63" t="s">
-        <v>346</v>
-      </c>
-      <c r="AD7" s="63" t="s">
-        <v>347</v>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD7" s="25" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -14032,41 +13916,41 @@
       <c r="K8" s="10">
         <v>75383</v>
       </c>
-      <c r="R8" s="64" t="s">
-        <v>342</v>
-      </c>
-      <c r="S8" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="T8" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="U8" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="V8" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="W8" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="X8" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="Y8" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="Z8" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="AA8" s="63" t="s">
-        <v>345</v>
-      </c>
-      <c r="AB8" s="63" t="s">
-        <v>348</v>
-      </c>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="63"/>
+      <c r="R8" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="S8" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="T8" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="U8" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="V8" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="W8" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="X8" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="Y8" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="Z8" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA8" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB8" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
     </row>
     <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
@@ -14102,35 +13986,35 @@
       <c r="K9" s="11">
         <v>1213212</v>
       </c>
-      <c r="R9" s="65" t="s">
+      <c r="R9" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" s="66">
+      <c r="S9" s="25"/>
+      <c r="T9" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="U9" s="28">
         <v>3497247</v>
       </c>
-      <c r="V9" s="63">
+      <c r="V9" s="25">
         <v>0.40004552152021289</v>
       </c>
-      <c r="W9" s="63"/>
-      <c r="X9" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y9" s="63"/>
-      <c r="Z9" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC9" s="66">
+      <c r="W9" s="25"/>
+      <c r="X9" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC9" s="28">
         <v>3497247</v>
       </c>
-      <c r="AD9" s="63">
+      <c r="AD9" s="25">
         <v>0.40004552152021289</v>
       </c>
     </row>
@@ -14168,35 +14052,35 @@
       <c r="K10" s="10">
         <v>195968</v>
       </c>
-      <c r="R10" s="65" t="s">
+      <c r="R10" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W10" s="63"/>
-      <c r="X10" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y10" s="66">
+      <c r="S10" s="25"/>
+      <c r="T10" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y10" s="28">
         <v>3808403</v>
       </c>
-      <c r="Z10" s="63">
+      <c r="Z10" s="25">
         <v>0.40003880891806881</v>
       </c>
-      <c r="AA10" s="63"/>
-      <c r="AB10" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC10" s="66">
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC10" s="28">
         <v>3808403</v>
       </c>
-      <c r="AD10" s="63">
+      <c r="AD10" s="25">
         <v>0.40003880891806881</v>
       </c>
     </row>
@@ -14234,35 +14118,35 @@
       <c r="K11" s="11">
         <v>209494</v>
       </c>
-      <c r="R11" s="65" t="s">
+      <c r="R11" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="S11" s="66">
+      <c r="S11" s="28">
         <v>3394020</v>
       </c>
-      <c r="T11" s="63">
+      <c r="T11" s="25">
         <v>0.4000509720037006</v>
       </c>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC11" s="66">
+      <c r="U11" s="25"/>
+      <c r="V11" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC11" s="28">
         <v>3394020</v>
       </c>
-      <c r="AD11" s="63">
+      <c r="AD11" s="25">
         <v>0.4000509720037006</v>
       </c>
     </row>
@@ -14301,35 +14185,35 @@
         <v>7956</v>
       </c>
       <c r="M12" s="23"/>
-      <c r="R12" s="65" t="s">
+      <c r="R12" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="S12" s="63"/>
-      <c r="T12" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U12" s="63"/>
-      <c r="V12" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W12" s="66">
+      <c r="S12" s="25"/>
+      <c r="T12" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="W12" s="28">
         <v>11357109</v>
       </c>
-      <c r="X12" s="63">
+      <c r="X12" s="25">
         <v>0.40002169566216189</v>
       </c>
-      <c r="Y12" s="63"/>
-      <c r="Z12" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA12" s="63"/>
-      <c r="AB12" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC12" s="66">
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC12" s="28">
         <v>11357109</v>
       </c>
-      <c r="AD12" s="63">
+      <c r="AD12" s="25">
         <v>0.40002169566216189</v>
       </c>
     </row>
@@ -14367,35 +14251,35 @@
       <c r="K13" s="11">
         <v>51372</v>
       </c>
-      <c r="R13" s="65" t="s">
+      <c r="R13" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U13" s="63"/>
-      <c r="V13" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W13" s="63"/>
-      <c r="X13" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y13" s="63"/>
-      <c r="Z13" s="63" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA13" s="66">
+      <c r="S13" s="25"/>
+      <c r="T13" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA13" s="28">
         <v>1230944</v>
       </c>
-      <c r="AB13" s="63">
+      <c r="AB13" s="25">
         <v>0.40013030649647752</v>
       </c>
-      <c r="AC13" s="66">
+      <c r="AC13" s="28">
         <v>1230944</v>
       </c>
-      <c r="AD13" s="63">
+      <c r="AD13" s="25">
         <v>0.40013030649647752</v>
       </c>
     </row>
@@ -14434,43 +14318,43 @@
         <v>157564</v>
       </c>
       <c r="N14" s="24"/>
-      <c r="R14" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="S14" s="66">
+      <c r="R14" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="S14" s="28">
         <v>3394020</v>
       </c>
-      <c r="T14" s="63">
+      <c r="T14" s="25">
         <v>0.4000509720037006</v>
       </c>
-      <c r="U14" s="66">
+      <c r="U14" s="28">
         <v>3497247</v>
       </c>
-      <c r="V14" s="63">
+      <c r="V14" s="25">
         <v>0.40004552152021289</v>
       </c>
-      <c r="W14" s="66">
+      <c r="W14" s="28">
         <v>11357109</v>
       </c>
-      <c r="X14" s="63">
+      <c r="X14" s="25">
         <v>0.40002169566216189</v>
       </c>
-      <c r="Y14" s="66">
+      <c r="Y14" s="28">
         <v>3808403</v>
       </c>
-      <c r="Z14" s="63">
+      <c r="Z14" s="25">
         <v>0.40003880891806881</v>
       </c>
-      <c r="AA14" s="66">
+      <c r="AA14" s="28">
         <v>1230944</v>
       </c>
-      <c r="AB14" s="63">
+      <c r="AB14" s="25">
         <v>0.40013030649647752</v>
       </c>
-      <c r="AC14" s="66">
+      <c r="AC14" s="28">
         <v>23287723</v>
       </c>
-      <c r="AD14" s="63">
+      <c r="AD14" s="25">
         <v>0.40003808015064418</v>
       </c>
     </row>
@@ -14546,7 +14430,7 @@
       </c>
       <c r="N16" s="24"/>
     </row>
-    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>11</v>
       </c>
@@ -14582,7 +14466,7 @@
       </c>
       <c r="N17" s="24"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>12</v>
       </c>
@@ -14618,7 +14502,7 @@
       </c>
       <c r="N18" s="24"/>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>13</v>
       </c>
@@ -14653,7 +14537,7 @@
         <v>36610</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>14</v>
       </c>
@@ -14688,7 +14572,7 @@
         <v>81576</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>15</v>
       </c>
@@ -14723,7 +14607,7 @@
         <v>4095</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
         <v>16</v>
       </c>
@@ -14758,7 +14642,7 @@
         <v>27080</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>17</v>
       </c>
@@ -14793,7 +14677,7 @@
         <v>17724</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
         <v>18</v>
       </c>
@@ -14828,7 +14712,7 @@
         <v>89940</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>19</v>
       </c>
@@ -14863,7 +14747,7 @@
         <v>8550</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
         <v>20</v>
       </c>
@@ -14898,7 +14782,7 @@
         <v>32103</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>21</v>
       </c>
@@ -14933,7 +14817,7 @@
         <v>37962</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
         <v>22</v>
       </c>
@@ -14968,7 +14852,7 @@
         <v>272768</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>23</v>
       </c>
@@ -15003,7 +14887,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
         <v>24</v>
       </c>
@@ -15038,7 +14922,7 @@
         <v>73917</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>25</v>
       </c>
@@ -15072,8 +14956,11 @@
       <c r="K31" s="11">
         <v>38038</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R31" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
         <v>26</v>
       </c>
@@ -17350,142 +17237,142 @@
     </row>
     <row r="98" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="99" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="26"/>
-      <c r="H99" s="26"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="27"/>
+      <c r="A99" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="30"/>
+      <c r="K99" s="31"/>
     </row>
     <row r="100" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="B100" s="43"/>
-      <c r="C100" s="43"/>
-      <c r="D100" s="43"/>
-      <c r="E100" s="43"/>
-      <c r="F100" s="43"/>
-      <c r="G100" s="43"/>
-      <c r="H100" s="43"/>
-      <c r="I100" s="43"/>
-      <c r="J100" s="43"/>
-      <c r="K100" s="34"/>
+      <c r="A100" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="39"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="39"/>
+      <c r="J100" s="39"/>
+      <c r="K100" s="40"/>
     </row>
     <row r="101" spans="1:11" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="B101" s="43"/>
-      <c r="C101" s="43"/>
-      <c r="D101" s="43"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43"/>
-      <c r="H101" s="43"/>
-      <c r="I101" s="43"/>
-      <c r="J101" s="43"/>
-      <c r="K101" s="34"/>
+      <c r="A101" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="39"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
+      <c r="H101" s="39"/>
+      <c r="I101" s="39"/>
+      <c r="J101" s="39"/>
+      <c r="K101" s="40"/>
     </row>
     <row r="102" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="103" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="B103" s="43"/>
-      <c r="C103" s="43"/>
-      <c r="D103" s="43"/>
-      <c r="E103" s="43"/>
-      <c r="F103" s="43"/>
-      <c r="G103" s="43"/>
-      <c r="H103" s="43"/>
-      <c r="I103" s="43"/>
-      <c r="J103" s="43"/>
-      <c r="K103" s="34"/>
+      <c r="A103" s="60" t="s">
+        <v>221</v>
+      </c>
+      <c r="B103" s="39"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
+      <c r="I103" s="39"/>
+      <c r="J103" s="39"/>
+      <c r="K103" s="40"/>
     </row>
     <row r="104" spans="1:11" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="B104" s="43"/>
-      <c r="C104" s="43"/>
-      <c r="D104" s="43"/>
-      <c r="E104" s="43"/>
-      <c r="F104" s="43"/>
-      <c r="G104" s="43"/>
-      <c r="H104" s="43"/>
-      <c r="I104" s="43"/>
-      <c r="J104" s="43"/>
-      <c r="K104" s="34"/>
+      <c r="A104" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="B104" s="39"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="39"/>
+      <c r="F104" s="39"/>
+      <c r="G104" s="39"/>
+      <c r="H104" s="39"/>
+      <c r="I104" s="39"/>
+      <c r="J104" s="39"/>
+      <c r="K104" s="40"/>
     </row>
     <row r="105" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="106" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="B106" s="43"/>
-      <c r="C106" s="43"/>
-      <c r="D106" s="43"/>
-      <c r="E106" s="43"/>
-      <c r="F106" s="43"/>
-      <c r="G106" s="43"/>
-      <c r="H106" s="43"/>
-      <c r="I106" s="43"/>
-      <c r="J106" s="43"/>
-      <c r="K106" s="34"/>
+      <c r="A106" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="B106" s="39"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="39"/>
+      <c r="I106" s="39"/>
+      <c r="J106" s="39"/>
+      <c r="K106" s="40"/>
     </row>
     <row r="107" spans="1:11" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="B107" s="43"/>
-      <c r="C107" s="43"/>
-      <c r="D107" s="43"/>
-      <c r="E107" s="43"/>
-      <c r="F107" s="43"/>
-      <c r="G107" s="43"/>
-      <c r="H107" s="43"/>
-      <c r="I107" s="43"/>
-      <c r="J107" s="43"/>
-      <c r="K107" s="34"/>
+      <c r="A107" s="38" t="s">
+        <v>223</v>
+      </c>
+      <c r="B107" s="39"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="39"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="39"/>
+      <c r="H107" s="39"/>
+      <c r="I107" s="39"/>
+      <c r="J107" s="39"/>
+      <c r="K107" s="40"/>
     </row>
     <row r="108" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="109" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="B109" s="43"/>
-      <c r="C109" s="43"/>
-      <c r="D109" s="43"/>
-      <c r="E109" s="43"/>
-      <c r="F109" s="43"/>
-      <c r="G109" s="43"/>
-      <c r="H109" s="43"/>
-      <c r="I109" s="43"/>
-      <c r="J109" s="43"/>
-      <c r="K109" s="34"/>
+      <c r="A109" s="60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B109" s="39"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="39"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="39"/>
+      <c r="H109" s="39"/>
+      <c r="I109" s="39"/>
+      <c r="J109" s="39"/>
+      <c r="K109" s="40"/>
     </row>
     <row r="110" spans="1:11" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="44" t="s">
-        <v>231</v>
-      </c>
-      <c r="B110" s="43"/>
-      <c r="C110" s="43"/>
-      <c r="D110" s="43"/>
-      <c r="E110" s="43"/>
-      <c r="F110" s="43"/>
-      <c r="G110" s="43"/>
-      <c r="H110" s="43"/>
-      <c r="I110" s="43"/>
-      <c r="J110" s="43"/>
-      <c r="K110" s="34"/>
+      <c r="A110" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B110" s="39"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="39"/>
+      <c r="I110" s="39"/>
+      <c r="J110" s="39"/>
+      <c r="K110" s="40"/>
     </row>
     <row r="111" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -17531,50 +17418,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
+      <c r="A1" s="54" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
+      <c r="A2" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="27"/>
+      <c r="A4" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="47"/>
+      <c r="A5" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B7" s="11">
         <v>20000000</v>
@@ -17582,7 +17469,7 @@
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B8" s="17">
         <v>1.2E-2</v>
@@ -17590,7 +17477,7 @@
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B9" s="11">
         <v>48</v>
@@ -17598,18 +17485,18 @@
     </row>
     <row r="10" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="34"/>
+      <c r="A11" s="60" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B12" s="14">
         <f>PMT(B8,B9,-B7)</f>
@@ -17617,50 +17504,50 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="34"/>
+      <c r="A13" s="60" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="34"/>
+      <c r="A14" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="1:6" ht="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="27"/>
+      <c r="A16" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:6" ht="185" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
+      <c r="A17" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59"/>
     </row>
     <row r="18" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B19" s="17">
         <v>0.14000000000000001</v>
@@ -17670,15 +17557,15 @@
     <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
       <c r="B21" s="5" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B22" s="11">
         <v>-9000000</v>
@@ -17689,7 +17576,7 @@
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B23" s="11">
         <v>2339951</v>
@@ -17700,7 +17587,7 @@
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B24" s="11">
         <v>2059930</v>
@@ -17711,7 +17598,7 @@
     </row>
     <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B25" s="11">
         <v>1997811</v>
@@ -17722,7 +17609,7 @@
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B26" s="11">
         <v>2791223</v>
@@ -17733,7 +17620,7 @@
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B27" s="11">
         <v>2799208</v>
@@ -17745,7 +17632,7 @@
     <row r="28" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B29" s="14">
         <f>NPV(B19,B23:B27)+B22</f>
@@ -17758,7 +17645,7 @@
     </row>
     <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B30" s="19">
         <f>IRR(B22:B27)</f>
@@ -17771,44 +17658,44 @@
     </row>
     <row r="31" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="34"/>
+      <c r="A32" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
     </row>
     <row r="33" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="34"/>
+      <c r="A33" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="40"/>
     </row>
     <row r="34" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="34"/>
+      <c r="A34" s="60" t="s">
+        <v>250</v>
+      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="40"/>
     </row>
     <row r="35" spans="1:6" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="44" t="s">
-        <v>259</v>
-      </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="34"/>
+      <c r="A35" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -17843,38 +17730,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27"/>
+      <c r="A1" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
+      <c r="A2" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="52" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -17893,7 +17780,7 @@
         <v>161</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18023,15 +17910,15 @@
     </row>
     <row r="12" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="27"/>
+      <c r="A13" s="52" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
@@ -18044,7 +17931,7 @@
         <v>129</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -18135,145 +18022,149 @@
     <row r="20" spans="1:7" ht="43" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:7" ht="251" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
+      <c r="A22" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="59"/>
     </row>
     <row r="23" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="49" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="27"/>
+      <c r="A24" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="27"/>
+      <c r="A26" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="42" t="s">
-        <v>269</v>
-      </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="34"/>
+      <c r="A27" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
     </row>
     <row r="28" spans="1:7" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="34"/>
+      <c r="A28" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
     </row>
     <row r="29" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="34"/>
+      <c r="A30" s="60" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
     </row>
     <row r="31" spans="1:7" ht="127" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="34"/>
+      <c r="A31" s="38" t="s">
+        <v>347</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
     </row>
     <row r="32" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="42" t="s">
-        <v>273</v>
-      </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="34"/>
+      <c r="A33" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="34"/>
+      <c r="A34" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="34"/>
+      <c r="A36" s="60" t="s">
+        <v>262</v>
+      </c>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="40"/>
     </row>
     <row r="37" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="34"/>
+      <c r="A37" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="40"/>
     </row>
     <row r="38" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="39" spans="1:7" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="27"/>
+      <c r="A39" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A34:G34"/>
@@ -18286,10 +18177,6 @@
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -18310,264 +18197,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>279</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
     </row>
     <row r="3" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="54" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
+      <c r="A4" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
-        <v>281</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27"/>
+      <c r="A5" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31"/>
     </row>
     <row r="6" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
-        <v>282</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27"/>
+      <c r="A7" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
     </row>
     <row r="8" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
     </row>
     <row r="9" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>288</v>
+        <v>273</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>290</v>
+        <v>275</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>292</v>
+        <v>277</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="B15" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="32" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>295</v>
+        <v>280</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="48" t="s">
-        <v>297</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="51" t="s">
-        <v>298</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="27"/>
+      <c r="A21" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
     </row>
     <row r="22" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="27"/>
+      <c r="A22" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="49" t="s">
-        <v>300</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="44"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="34"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
     </row>
     <row r="25" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="51" t="s">
-        <v>301</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
+      <c r="A26" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
     </row>
     <row r="27" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
+      <c r="A27" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="49" t="s">
-        <v>300</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
+      <c r="A28" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
     </row>
     <row r="29" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="44"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="34"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
     </row>
     <row r="30" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
+      <c r="A31" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
     </row>
     <row r="32" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="50" t="s">
-        <v>304</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
+      <c r="A32" s="37" t="s">
+        <v>290</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="31"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="49" t="s">
-        <v>300</v>
-      </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
+      <c r="A33" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="31"/>
     </row>
     <row r="34" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="44"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="34"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
     </row>
     <row r="35" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
+      <c r="A36" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
     </row>
     <row r="37" spans="1:3" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
-        <v>306</v>
-      </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
+      <c r="A37" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="49" t="s">
-        <v>300</v>
-      </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" s="30"/>
+      <c r="C38" s="31"/>
     </row>
     <row r="39" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="44"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="34"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="40"/>
     </row>
     <row r="40" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="41" spans="1:3" ht="44" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
+      <c r="A41" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="B12"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="B14"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="B15"/>
@@ -18580,6 +18446,27 @@
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
